--- a/src/attributions/attributions_saliency_traj_255.xlsx
+++ b/src/attributions/attributions_saliency_traj_255.xlsx
@@ -999,5692 +999,5692 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.890180909773335e-05</v>
+        <v>9.147656237473711e-05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0004047733964398503</v>
+        <v>0.0002019085659412667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001063948438968509</v>
+        <v>5.234166019363329e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003985939838457853</v>
+        <v>0.0001584794226801023</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0001226250897161663</v>
+        <v>4.995112612959929e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002748775877989829</v>
+        <v>0.0001298127317568287</v>
       </c>
       <c r="G2" t="n">
-        <v>3.038673457922414e-05</v>
+        <v>5.282936035655439e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.319768645975273e-05</v>
+        <v>2.510618833184708e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>4.844402428716421e-05</v>
+        <v>1.013476230582455e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.003194483928382e-05</v>
+        <v>0.0001602871780050918</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003914049593731761</v>
+        <v>0.0002165112091461197</v>
       </c>
       <c r="L2" t="n">
-        <v>3.124296927126125e-05</v>
+        <v>0.000100509547337424</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003034206747543067</v>
+        <v>0.0002146499464288354</v>
       </c>
       <c r="N2" t="n">
-        <v>7.012781861703843e-05</v>
+        <v>8.977048855740577e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001229854533448815</v>
+        <v>9.339532698504627e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>5.298647010931745e-06</v>
+        <v>6.487410428235307e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.910748844442423e-05</v>
+        <v>7.401954007946188e-06</v>
       </c>
       <c r="R2" t="n">
-        <v>6.380787090165541e-05</v>
+        <v>3.764640860026702e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>3.46063170582056e-05</v>
+        <v>3.991036646766588e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.909870636358391e-05</v>
+        <v>5.578223499469459e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>2.574531026766635e-05</v>
+        <v>4.402544618642423e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.000120838129078038</v>
+        <v>4.12940644309856e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>6.71451780362986e-05</v>
+        <v>1.430272550351219e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>2.131653127435129e-05</v>
+        <v>4.815417560166679e-05</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.326757334638387e-07</v>
+        <v>2.546715677453903e-06</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.130520558945136e-05</v>
+        <v>1.656330823607277e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.141798384196591e-05</v>
+        <v>1.501529823144665e-05</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.779340451932512e-05</v>
+        <v>3.396510692255106e-06</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.292168862069957e-05</v>
+        <v>2.88393330265535e-05</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.310236050107051e-05</v>
+        <v>3.025449950655457e-05</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0001501980441389605</v>
+        <v>6.238338391995057e-05</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.046202229801565e-05</v>
+        <v>1.376610453007743e-05</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.31806149915792e-05</v>
+        <v>7.769556759740226e-06</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.916267814929597e-06</v>
+        <v>1.529664223198779e-05</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.094038897368591e-06</v>
+        <v>7.79937363404315e-06</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5.090104968985543e-05</v>
+        <v>8.121498467517085e-06</v>
       </c>
       <c r="AK2" t="n">
-        <v>7.053394256217871e-06</v>
+        <v>2.175705594709143e-05</v>
       </c>
       <c r="AL2" t="n">
-        <v>9.520274761598557e-05</v>
+        <v>2.699001197470352e-05</v>
       </c>
       <c r="AM2" t="n">
-        <v>7.306478892132873e-06</v>
+        <v>5.585653525486123e-06</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.808123776456341e-05</v>
+        <v>1.956973937922157e-05</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.763934392329247e-06</v>
+        <v>5.216507270233706e-05</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0001053243831847794</v>
+        <v>5.436657738755457e-05</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.349212288914714e-05</v>
+        <v>1.09665488707833e-05</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.066043063881807e-05</v>
+        <v>5.606040758721065e-06</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.259573739138432e-05</v>
+        <v>8.971239367383532e-06</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.0048522350844e-05</v>
+        <v>5.135565515956841e-06</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.0001847479288699105</v>
+        <v>0.0001412008132319897</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.816922981059179e-05</v>
+        <v>2.755205787252635e-05</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0001972728641703725</v>
+        <v>0.0001122993417084217</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.674855063058203e-07</v>
+        <v>2.237654189229943e-05</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0001711037330096588</v>
+        <v>1.784776759450324e-05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.791784936562181e-08</v>
+        <v>5.009083906770684e-06</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.317533552646637e-05</v>
+        <v>1.543894768474274e-06</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.769938146229833e-05</v>
+        <v>1.958084249054082e-05</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.122807124280371e-06</v>
+        <v>1.393893762724474e-05</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.377079211641103e-05</v>
+        <v>3.932081745006144e-05</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.042478682706133e-05</v>
+        <v>5.213782424107194e-05</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0001577557704877108</v>
+        <v>2.792429222608916e-05</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.25855430169031e-05</v>
+        <v>2.577997292974032e-05</v>
       </c>
       <c r="BH2" t="n">
-        <v>6.905225745867938e-05</v>
+        <v>3.230291986255907e-05</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.557891664560884e-06</v>
+        <v>5.631552267004736e-05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.019325079862028e-05</v>
+        <v>5.388857607613318e-05</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.086196349817328e-05</v>
+        <v>4.590995376929641e-05</v>
       </c>
       <c r="BL2" t="n">
-        <v>6.308727461146191e-05</v>
+        <v>8.900207831175067e-06</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.377028067712672e-06</v>
+        <v>5.871491521247663e-05</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.998225580900908e-05</v>
+        <v>3.834890958387405e-05</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.391504626255482e-05</v>
+        <v>1.226790845976211e-05</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.945674299960956e-05</v>
+        <v>3.935401309718145e-06</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.785551077977289e-05</v>
+        <v>2.141318873327691e-05</v>
       </c>
       <c r="BR2" t="n">
-        <v>2.973646769532934e-05</v>
+        <v>3.934054257115349e-05</v>
       </c>
       <c r="BS2" t="n">
-        <v>4.077015182701871e-05</v>
+        <v>2.866160139092244e-05</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.07146944780834e-05</v>
+        <v>2.126573053828906e-05</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0001292170927627012</v>
+        <v>6.472363020293415e-05</v>
       </c>
       <c r="BV2" t="n">
-        <v>3.899255898431875e-05</v>
+        <v>0.0001147381699411198</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.649399903020822e-05</v>
+        <v>4.17799174101674e-06</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.00012658053310588</v>
+        <v>2.533631050027907e-05</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.407453328283736e-05</v>
+        <v>2.55954910244327e-05</v>
       </c>
       <c r="BZ2" t="n">
-        <v>5.974952728138305e-07</v>
+        <v>8.12974976724945e-05</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.292725573875941e-05</v>
+        <v>2.796222361212131e-05</v>
       </c>
       <c r="CB2" t="n">
-        <v>6.231231964193285e-05</v>
+        <v>1.948255885508843e-05</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.656696076679509e-05</v>
+        <v>8.225708370446227e-06</v>
       </c>
       <c r="CD2" t="n">
-        <v>9.444946954317857e-06</v>
+        <v>1.132198030973086e-05</v>
       </c>
       <c r="CE2" t="n">
-        <v>5.014116686652415e-05</v>
+        <v>5.047511149314232e-05</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.494505315553397e-05</v>
+        <v>3.138616011710837e-05</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0001036534813465551</v>
+        <v>3.926577846868895e-05</v>
       </c>
       <c r="CH2" t="n">
-        <v>4.290337165002711e-05</v>
+        <v>2.757217544058221e-06</v>
       </c>
       <c r="CI2" t="n">
-        <v>3.398004309929092e-06</v>
+        <v>3.793832092924276e-07</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.083778053929564e-05</v>
+        <v>1.100984263757709e-07</v>
       </c>
       <c r="CK2" t="n">
-        <v>2.290246811753605e-05</v>
+        <v>2.307845534232911e-05</v>
       </c>
       <c r="CL2" t="n">
-        <v>8.606380106357392e-06</v>
+        <v>8.905321010388434e-06</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.901263203762937e-06</v>
+        <v>7.625923171872273e-05</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0001474760647397488</v>
+        <v>1.235052604897646e-05</v>
       </c>
       <c r="CO2" t="n">
-        <v>4.869614713243209e-05</v>
+        <v>2.502753886801656e-05</v>
       </c>
       <c r="CP2" t="n">
-        <v>8.564514428144321e-05</v>
+        <v>0.0001064411044353619</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.195290992152877e-05</v>
+        <v>4.682972939917818e-05</v>
       </c>
       <c r="CR2" t="n">
-        <v>8.487821469316259e-05</v>
+        <v>2.420967030047905e-05</v>
       </c>
       <c r="CS2" t="n">
-        <v>7.143728726077825e-05</v>
+        <v>2.127946117980173e-06</v>
       </c>
       <c r="CT2" t="n">
-        <v>1.476638226449722e-05</v>
+        <v>2.918634527304675e-05</v>
       </c>
       <c r="CU2" t="n">
-        <v>9.097539077629335e-06</v>
+        <v>3.695484701893292e-05</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.108109518099809e-05</v>
+        <v>9.682980817160569e-06</v>
       </c>
       <c r="CW2" t="n">
-        <v>6.6302643972449e-05</v>
+        <v>5.990774297970347e-05</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.894049637485296e-05</v>
+        <v>2.897569720516913e-05</v>
       </c>
       <c r="CY2" t="n">
-        <v>9.900217992253602e-05</v>
+        <v>5.13020931975916e-05</v>
       </c>
       <c r="CZ2" t="n">
-        <v>3.819082485279068e-05</v>
+        <v>1.467967013013549e-05</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.499727386544691e-05</v>
+        <v>1.013658766169101e-05</v>
       </c>
       <c r="DB2" t="n">
-        <v>3.1090898119146e-05</v>
+        <v>1.08281446955516e-05</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.753636934154201e-05</v>
+        <v>2.123079502780456e-05</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.818768942030147e-05</v>
+        <v>5.645557848765748e-06</v>
       </c>
       <c r="DE2" t="n">
-        <v>5.65175578230992e-05</v>
+        <v>1.37354136313661e-05</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.0002135205140803009</v>
+        <v>5.035992217017338e-05</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.0001318103750236332</v>
+        <v>4.747063940158114e-05</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.0001432990247849375</v>
+        <v>2.740322452154942e-05</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0003225968685001135</v>
+        <v>5.506529487320222e-05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0001381993643008173</v>
+        <v>5.080096889287233e-05</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.811878145323135e-05</v>
+        <v>4.931457169732312e-06</v>
       </c>
       <c r="DL2" t="n">
-        <v>3.258463402744383e-05</v>
+        <v>5.462019908009097e-05</v>
       </c>
       <c r="DM2" t="n">
-        <v>4.115293450013269e-06</v>
+        <v>2.848790427378844e-05</v>
       </c>
       <c r="DN2" t="n">
-        <v>2.223879891971592e-05</v>
+        <v>2.166671947634313e-05</v>
       </c>
       <c r="DO2" t="n">
-        <v>7.67451201681979e-05</v>
+        <v>4.204959986964241e-05</v>
       </c>
       <c r="DP2" t="n">
-        <v>5.623503238894045e-05</v>
+        <v>3.889176150551066e-05</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.0001202148414449766</v>
+        <v>3.981251211371273e-05</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0001079983630916104</v>
+        <v>3.160043706884608e-05</v>
       </c>
       <c r="DS2" t="n">
-        <v>2.492552084731869e-05</v>
+        <v>6.695288902847096e-05</v>
       </c>
       <c r="DT2" t="n">
-        <v>3.46613087458536e-05</v>
+        <v>1.330179657088593e-05</v>
       </c>
       <c r="DU2" t="n">
-        <v>6.138565368019044e-05</v>
+        <v>6.633635166508611e-06</v>
       </c>
       <c r="DV2" t="n">
-        <v>2.66428614850156e-05</v>
+        <v>6.844184827059507e-05</v>
       </c>
       <c r="DW2" t="n">
-        <v>2.495349144737702e-05</v>
+        <v>1.353202787868213e-05</v>
       </c>
       <c r="DX2" t="n">
-        <v>3.679597284644842e-07</v>
+        <v>2.314419361937325e-06</v>
       </c>
       <c r="DY2" t="n">
-        <v>1.52284737851005e-05</v>
+        <v>9.272954230254982e-06</v>
       </c>
       <c r="DZ2" t="n">
-        <v>7.540031947428361e-05</v>
+        <v>2.250848046969622e-05</v>
       </c>
       <c r="EA2" t="n">
-        <v>5.977682667435147e-05</v>
+        <v>5.623023753287271e-05</v>
       </c>
       <c r="EB2" t="n">
-        <v>8.054206409724429e-05</v>
+        <v>2.059785219898913e-05</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.277759449498262e-05</v>
+        <v>1.419113141309936e-05</v>
       </c>
       <c r="ED2" t="n">
-        <v>2.169917934224941e-07</v>
+        <v>4.310472650104202e-05</v>
       </c>
       <c r="EE2" t="n">
-        <v>2.139530079148244e-05</v>
+        <v>4.393011113279499e-05</v>
       </c>
       <c r="EF2" t="n">
-        <v>7.033230212982744e-05</v>
+        <v>1.063614035956562e-06</v>
       </c>
       <c r="EG2" t="n">
-        <v>3.661367736640386e-05</v>
+        <v>2.147891063941643e-05</v>
       </c>
       <c r="EH2" t="n">
-        <v>1.817146403482184e-05</v>
+        <v>1.384183997288346e-05</v>
       </c>
       <c r="EI2" t="n">
-        <v>3.09207352984231e-05</v>
+        <v>5.285687075229362e-05</v>
       </c>
       <c r="EJ2" t="n">
-        <v>2.144685822713654e-05</v>
+        <v>2.986638264701469e-06</v>
       </c>
       <c r="EK2" t="n">
-        <v>3.147724783048034e-05</v>
+        <v>2.338470403628889e-05</v>
       </c>
       <c r="EL2" t="n">
-        <v>1.417355269950349e-05</v>
+        <v>3.220617145416327e-06</v>
       </c>
       <c r="EM2" t="n">
-        <v>1.817747943277936e-05</v>
+        <v>2.518132532713935e-05</v>
       </c>
       <c r="EN2" t="n">
-        <v>3.867510531563312e-05</v>
+        <v>1.7606205346965e-06</v>
       </c>
       <c r="EO2" t="n">
-        <v>2.866631621145643e-05</v>
+        <v>6.949429007363506e-06</v>
       </c>
       <c r="EP2" t="n">
-        <v>1.322076332144206e-05</v>
+        <v>4.135213021072559e-05</v>
       </c>
       <c r="EQ2" t="n">
-        <v>4.141413592151366e-05</v>
+        <v>3.564919461496174e-05</v>
       </c>
       <c r="ER2" t="n">
-        <v>1.828408312576357e-05</v>
+        <v>2.023801607720088e-05</v>
       </c>
       <c r="ES2" t="n">
-        <v>5.033117122366093e-05</v>
+        <v>2.107646469085012e-05</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.0001089387151296251</v>
+        <v>7.361765892710537e-05</v>
       </c>
       <c r="EU2" t="n">
-        <v>1.076343323802575e-05</v>
+        <v>3.799441765295342e-05</v>
       </c>
       <c r="EV2" t="n">
-        <v>6.754473724868149e-05</v>
+        <v>2.727065111685079e-05</v>
       </c>
       <c r="EW2" t="n">
-        <v>3.349588223500177e-05</v>
+        <v>3.80008204956539e-05</v>
       </c>
       <c r="EX2" t="n">
-        <v>2.743571531027555e-05</v>
+        <v>1.39360417961143e-05</v>
       </c>
       <c r="EY2" t="n">
-        <v>3.727818329934962e-05</v>
+        <v>5.670979589922354e-05</v>
       </c>
       <c r="EZ2" t="n">
-        <v>4.207797610433772e-05</v>
+        <v>2.032857810263522e-05</v>
       </c>
       <c r="FA2" t="n">
-        <v>8.946705929702148e-05</v>
+        <v>5.298876931192353e-05</v>
       </c>
       <c r="FB2" t="n">
-        <v>8.746838830120396e-06</v>
+        <v>1.490021168137901e-05</v>
       </c>
       <c r="FC2" t="n">
-        <v>2.769940329017118e-05</v>
+        <v>5.646887984767091e-06</v>
       </c>
       <c r="FD2" t="n">
-        <v>2.040689469140489e-05</v>
+        <v>1.976142357307253e-06</v>
       </c>
       <c r="FE2" t="n">
-        <v>3.614176603150554e-05</v>
+        <v>1.550012348161545e-05</v>
       </c>
       <c r="FF2" t="n">
-        <v>1.487585905124433e-05</v>
+        <v>5.706330739485566e-06</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.0001098893990274519</v>
+        <v>1.762539613991976e-05</v>
       </c>
       <c r="FH2" t="n">
-        <v>3.627939440775663e-05</v>
+        <v>4.642189742298797e-05</v>
       </c>
       <c r="FI2" t="n">
-        <v>8.47705450723879e-05</v>
+        <v>1.333977525064256e-05</v>
       </c>
       <c r="FJ2" t="n">
-        <v>3.72957656509243e-05</v>
+        <v>6.713382390444167e-06</v>
       </c>
       <c r="FK2" t="n">
-        <v>6.70888994136476e-06</v>
+        <v>7.124005787773058e-05</v>
       </c>
       <c r="FL2" t="n">
-        <v>1.087711916625267e-05</v>
+        <v>3.083550836890936e-05</v>
       </c>
       <c r="FM2" t="n">
-        <v>7.684890078962781e-06</v>
+        <v>3.504111373331398e-05</v>
       </c>
       <c r="FN2" t="n">
-        <v>6.424410821637139e-05</v>
+        <v>2.260200017190073e-05</v>
       </c>
       <c r="FO2" t="n">
-        <v>1.851095839811023e-05</v>
+        <v>2.127188963640947e-06</v>
       </c>
       <c r="FP2" t="n">
-        <v>7.339516741922125e-05</v>
+        <v>1.119817716244143e-05</v>
       </c>
       <c r="FQ2" t="n">
-        <v>6.891339580761269e-05</v>
+        <v>5.674463318428025e-05</v>
       </c>
       <c r="FR2" t="n">
-        <v>7.117021596059203e-05</v>
+        <v>6.705521082039922e-05</v>
       </c>
       <c r="FS2" t="n">
-        <v>1.046259967552032e-05</v>
+        <v>0.0001973239122889936</v>
       </c>
       <c r="FT2" t="n">
-        <v>4.313039244152606e-05</v>
+        <v>7.077659574861173e-06</v>
       </c>
       <c r="FU2" t="n">
-        <v>3.578827454475686e-05</v>
+        <v>1.678218359302264e-05</v>
       </c>
       <c r="FV2" t="n">
-        <v>1.034345768857747e-05</v>
+        <v>7.402153278235346e-05</v>
       </c>
       <c r="FW2" t="n">
-        <v>1.985620292543899e-05</v>
+        <v>3.948396988562308e-05</v>
       </c>
       <c r="FX2" t="n">
-        <v>1.26721388369333e-05</v>
+        <v>1.457064172427636e-05</v>
       </c>
       <c r="FY2" t="n">
-        <v>3.646543336799368e-05</v>
+        <v>2.934687108790968e-05</v>
       </c>
       <c r="FZ2" t="n">
-        <v>3.371464845258743e-05</v>
+        <v>6.580675835721195e-05</v>
       </c>
       <c r="GA2" t="n">
-        <v>1.394123137288261e-05</v>
+        <v>2.442830918880645e-05</v>
       </c>
       <c r="GB2" t="n">
-        <v>5.13214290549513e-05</v>
+        <v>3.178253246005625e-05</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.0002249566314276308</v>
+        <v>4.82469258713536e-05</v>
       </c>
       <c r="GD2" t="n">
-        <v>6.315037899184972e-05</v>
+        <v>6.923235196154565e-05</v>
       </c>
       <c r="GE2" t="n">
-        <v>5.990377758280374e-05</v>
+        <v>6.136752926977351e-05</v>
       </c>
       <c r="GF2" t="n">
-        <v>8.268890815088525e-05</v>
+        <v>4.328878640080802e-05</v>
       </c>
       <c r="GG2" t="n">
-        <v>1.573789631947875e-05</v>
+        <v>2.389686778769828e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.447947787866724e-09</v>
+        <v>3.399212022969778e-09</v>
       </c>
       <c r="B3" t="n">
-        <v>1.877490340973509e-08</v>
+        <v>8.596551026585075e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>8.546280350074653e-11</v>
+        <v>6.102502059235348e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.900206747507127e-08</v>
+        <v>9.100719067234309e-10</v>
       </c>
       <c r="E3" t="n">
-        <v>2.427917866754115e-09</v>
+        <v>2.400271981173319e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>2.562860812460599e-09</v>
+        <v>1.525098092258759e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.215305272557089e-09</v>
+        <v>3.838880324735783e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.775083883856723e-09</v>
+        <v>4.722178648108866e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.084477200905212e-11</v>
+        <v>3.934135239802572e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>5.575553352343832e-09</v>
+        <v>7.943883884031777e-10</v>
       </c>
       <c r="K3" t="n">
-        <v>1.330934207288692e-08</v>
+        <v>1.090962697958275e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.109874137039668e-10</v>
+        <v>7.264651102900643e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.062771559645626e-08</v>
+        <v>2.442677393688086e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>5.843719286247051e-09</v>
+        <v>1.033816765527718e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.127673421308373e-08</v>
+        <v>1.276993266685622e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>5.868458163860168e-09</v>
+        <v>3.101398027283153e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.178596466734689e-09</v>
+        <v>2.881722194203462e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>2.245759134211767e-12</v>
+        <v>2.925684139398754e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.806714222674088e-10</v>
+        <v>3.825413763536289e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.903661920963032e-09</v>
+        <v>1.466480492595679e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.708948538237109e-09</v>
+        <v>4.520837038057834e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.346430744675331e-10</v>
+        <v>4.66421679057305e-10</v>
       </c>
       <c r="W3" t="n">
-        <v>6.911495820105529e-09</v>
+        <v>3.812986371087845e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>4.568038391994378e-09</v>
+        <v>5.819333903644974e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.555195858875095e-09</v>
+        <v>2.975034663066367e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.977477567422397e-10</v>
+        <v>1.8421695280324e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.751180699396173e-09</v>
+        <v>5.583885784310461e-11</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.959132938684661e-10</v>
+        <v>1.262180360228626e-09</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.546938546847514e-10</v>
+        <v>3.549728067042679e-09</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.107409719480756e-09</v>
+        <v>2.519352504393169e-09</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.662028070725796e-09</v>
+        <v>3.631269951398508e-09</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.277783295312474e-09</v>
+        <v>6.639131466812387e-10</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.385879049882078e-09</v>
+        <v>3.518479507746974e-09</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.223719570120352e-09</v>
+        <v>6.494551563207551e-10</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.71535069376705e-09</v>
+        <v>9.897750175014153e-09</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.343737121572985e-09</v>
+        <v>9.943941225998287e-10</v>
       </c>
       <c r="AK3" t="n">
-        <v>4.862223956791922e-10</v>
+        <v>4.238164041936443e-09</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.739984766326643e-09</v>
+        <v>5.636522359964147e-10</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.111773226929017e-10</v>
+        <v>5.365648370059262e-09</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.143103694507431e-09</v>
+        <v>3.07559622214626e-09</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.784789427361488e-09</v>
+        <v>2.990921510459543e-09</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.379713010507544e-09</v>
+        <v>4.226116345762421e-09</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.613621541414091e-09</v>
+        <v>1.511771818840657e-10</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.285454575063795e-09</v>
+        <v>1.343820499322135e-09</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.793334230588584e-09</v>
+        <v>1.763939105892121e-09</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.544958326884284e-09</v>
+        <v>2.520703201724928e-09</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.198220722642418e-08</v>
+        <v>1.196466659081352e-08</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.230994639556116e-09</v>
+        <v>9.074150320032004e-09</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199165873496895e-09</v>
+        <v>2.238045748725881e-09</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.000266923791628e-09</v>
+        <v>1.145643313549272e-08</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.342243645349413e-11</v>
+        <v>1.200364785347574e-08</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.927815571737938e-09</v>
+        <v>1.949003403112215e-09</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.570780255339855e-09</v>
+        <v>2.165734258596785e-10</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.477881538316296e-09</v>
+        <v>7.92820753492407e-10</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.237205697421587e-09</v>
+        <v>4.141838427784705e-09</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.223946081793883e-09</v>
+        <v>1.661736304114925e-10</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.131256226003188e-09</v>
+        <v>4.32942570682826e-12</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.394276776840343e-09</v>
+        <v>3.875156640020805e-09</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.644406110225873e-09</v>
+        <v>8.257520889287662e-09</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.122632596941344e-09</v>
+        <v>3.067464060535485e-10</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.438450996677943e-09</v>
+        <v>4.213759563498343e-09</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.825234765197365e-09</v>
+        <v>5.247378975781203e-09</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.513437708489107e-09</v>
+        <v>9.022572688976993e-10</v>
       </c>
       <c r="BL3" t="n">
-        <v>3.345490995343425e-09</v>
+        <v>2.615347050038963e-09</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.076057548094923e-09</v>
+        <v>5.408256065209116e-09</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.485371324885023e-09</v>
+        <v>5.32423327648246e-10</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.64348346043397e-09</v>
+        <v>3.789121238995108e-10</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.546168300289537e-10</v>
+        <v>5.064094477091885e-09</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.536961751786748e-10</v>
+        <v>2.701813661687424e-09</v>
       </c>
       <c r="BR3" t="n">
-        <v>2.092875206471945e-09</v>
+        <v>2.487089645342166e-09</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.359223927328458e-13</v>
+        <v>1.949304939685703e-09</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.971027088908954e-10</v>
+        <v>2.368591711654489e-10</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.093419244035942e-10</v>
+        <v>2.337723126188962e-09</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.355716480361707e-09</v>
+        <v>4.681695919828144e-09</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.800941840102155e-09</v>
+        <v>5.470329078605118e-09</v>
       </c>
       <c r="BX3" t="n">
-        <v>2.861223258321388e-09</v>
+        <v>7.31955218657987e-10</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.779120349989284e-10</v>
+        <v>4.674352016564853e-09</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.594874232679899e-09</v>
+        <v>8.16553047400248e-09</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.43544370728921e-09</v>
+        <v>3.891810429479392e-09</v>
       </c>
       <c r="CB3" t="n">
-        <v>1.80589465603731e-09</v>
+        <v>5.595607310837636e-11</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.197856646153241e-09</v>
+        <v>5.894330579181428e-10</v>
       </c>
       <c r="CD3" t="n">
-        <v>8.698500253423447e-10</v>
+        <v>1.435337293465011e-09</v>
       </c>
       <c r="CE3" t="n">
-        <v>2.794811937434361e-09</v>
+        <v>3.556092975642855e-09</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.843695057208606e-09</v>
+        <v>8.17445999778954e-10</v>
       </c>
       <c r="CG3" t="n">
-        <v>1.136629124154354e-09</v>
+        <v>3.605750142909869e-10</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.402159832686323e-09</v>
+        <v>8.258591033261098e-10</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.384991121788914e-09</v>
+        <v>2.539364718501247e-09</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.195597232328538e-10</v>
+        <v>6.702285393345164e-10</v>
       </c>
       <c r="CK3" t="n">
-        <v>8.938647044764991e-11</v>
+        <v>1.081307043904189e-09</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.838802970472898e-09</v>
+        <v>2.621526606905178e-11</v>
       </c>
       <c r="CM3" t="n">
-        <v>5.472966524422418e-10</v>
+        <v>2.307071200746691e-10</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.767511248473852e-09</v>
+        <v>7.967732251756843e-09</v>
       </c>
       <c r="CO3" t="n">
-        <v>4.899236571986876e-11</v>
+        <v>5.610866882221899e-09</v>
       </c>
       <c r="CP3" t="n">
-        <v>3.01142777381358e-09</v>
+        <v>3.037033735608929e-09</v>
       </c>
       <c r="CQ3" t="n">
-        <v>1.309706565422175e-09</v>
+        <v>1.576950015014233e-09</v>
       </c>
       <c r="CR3" t="n">
-        <v>3.595424402647041e-09</v>
+        <v>1.170590291366125e-09</v>
       </c>
       <c r="CS3" t="n">
-        <v>5.308070871734571e-09</v>
+        <v>2.301592916253981e-09</v>
       </c>
       <c r="CT3" t="n">
-        <v>5.483650866722201e-09</v>
+        <v>3.306718898699046e-09</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.800724347411631e-09</v>
+        <v>2.153465405996258e-09</v>
       </c>
       <c r="CV3" t="n">
-        <v>9.991851790402961e-10</v>
+        <v>2.594024772761827e-09</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.236954843581884e-09</v>
+        <v>3.465542519620612e-09</v>
       </c>
       <c r="CX3" t="n">
-        <v>2.308186308752624e-09</v>
+        <v>1.366119439794033e-09</v>
       </c>
       <c r="CY3" t="n">
-        <v>3.325459463354719e-09</v>
+        <v>4.87587692443725e-10</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.287322248799683e-09</v>
+        <v>1.325492049453203e-09</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.952338735122794e-09</v>
+        <v>2.754878991595433e-09</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.134871446290987e-10</v>
+        <v>8.745338897497845e-10</v>
       </c>
       <c r="DC3" t="n">
-        <v>4.184405044682649e-10</v>
+        <v>4.129047381784545e-10</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.920359649076886e-09</v>
+        <v>9.687503577104906e-11</v>
       </c>
       <c r="DE3" t="n">
-        <v>4.85571582942157e-11</v>
+        <v>1.536536009538736e-09</v>
       </c>
       <c r="DF3" t="n">
-        <v>4.37068964354026e-10</v>
+        <v>3.780713520029622e-09</v>
       </c>
       <c r="DG3" t="n">
-        <v>9.706623060878883e-09</v>
+        <v>5.628835175741642e-10</v>
       </c>
       <c r="DH3" t="n">
-        <v>1.914118641366258e-08</v>
+        <v>1.231952984070972e-09</v>
       </c>
       <c r="DI3" t="n">
-        <v>1.465028098834864e-08</v>
+        <v>1.120540993326813e-09</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.5815426746002e-09</v>
+        <v>5.595706120686827e-09</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.030306672258121e-09</v>
+        <v>2.913939978199664e-09</v>
       </c>
       <c r="DL3" t="n">
-        <v>1.153933748554437e-08</v>
+        <v>3.937831838385364e-09</v>
       </c>
       <c r="DM3" t="n">
-        <v>1.310100139484405e-09</v>
+        <v>1.581289099661376e-09</v>
       </c>
       <c r="DN3" t="n">
-        <v>8.030790477064897e-10</v>
+        <v>2.76559597445214e-09</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.566829777033263e-09</v>
+        <v>2.14156758993056e-09</v>
       </c>
       <c r="DP3" t="n">
-        <v>2.890915062891963e-09</v>
+        <v>2.274764820953123e-10</v>
       </c>
       <c r="DQ3" t="n">
-        <v>3.436443352100582e-10</v>
+        <v>2.85310308711928e-09</v>
       </c>
       <c r="DR3" t="n">
-        <v>1.576474617515089e-09</v>
+        <v>2.968456869201219e-10</v>
       </c>
       <c r="DS3" t="n">
-        <v>2.653687714015973e-09</v>
+        <v>2.169566304388582e-09</v>
       </c>
       <c r="DT3" t="n">
-        <v>1.955768436090466e-09</v>
+        <v>2.324895609362443e-09</v>
       </c>
       <c r="DU3" t="n">
-        <v>8.873431989186997e-10</v>
+        <v>4.89558216187902e-09</v>
       </c>
       <c r="DV3" t="n">
-        <v>7.137784585609097e-09</v>
+        <v>1.783886705020166e-09</v>
       </c>
       <c r="DW3" t="n">
-        <v>2.344574312473924e-09</v>
+        <v>2.006478538874035e-09</v>
       </c>
       <c r="DX3" t="n">
-        <v>3.839728979215806e-09</v>
+        <v>2.367449125628696e-09</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.811071985244553e-09</v>
+        <v>3.02441538480025e-09</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.612560418529085e-09</v>
+        <v>1.499121049519658e-09</v>
       </c>
       <c r="EA3" t="n">
-        <v>1.587736830899189e-09</v>
+        <v>4.155276123185558e-09</v>
       </c>
       <c r="EB3" t="n">
-        <v>5.845993911179903e-09</v>
+        <v>1.490908507761901e-10</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.07988648526225e-09</v>
+        <v>2.402544829749331e-10</v>
       </c>
       <c r="ED3" t="n">
-        <v>1.939810756468319e-09</v>
+        <v>4.117586271945584e-09</v>
       </c>
       <c r="EE3" t="n">
-        <v>7.129443702069693e-10</v>
+        <v>3.099128731420819e-09</v>
       </c>
       <c r="EF3" t="n">
-        <v>7.144094205102647e-10</v>
+        <v>9.648468690670597e-10</v>
       </c>
       <c r="EG3" t="n">
-        <v>2.452622549498074e-10</v>
+        <v>1.875976707310656e-09</v>
       </c>
       <c r="EH3" t="n">
-        <v>5.544760206532828e-10</v>
+        <v>1.401838645165299e-09</v>
       </c>
       <c r="EI3" t="n">
-        <v>1.175837316402806e-09</v>
+        <v>1.039500707733509e-10</v>
       </c>
       <c r="EJ3" t="n">
-        <v>2.370411422703e-09</v>
+        <v>3.85635468003187e-10</v>
       </c>
       <c r="EK3" t="n">
-        <v>2.211862248913121e-09</v>
+        <v>2.063605730739937e-09</v>
       </c>
       <c r="EL3" t="n">
-        <v>5.110794010221298e-10</v>
+        <v>1.411582850607829e-09</v>
       </c>
       <c r="EM3" t="n">
-        <v>1.698653218085155e-09</v>
+        <v>4.456149060860781e-10</v>
       </c>
       <c r="EN3" t="n">
-        <v>1.275057948113556e-09</v>
+        <v>1.716261577300315e-09</v>
       </c>
       <c r="EO3" t="n">
-        <v>5.42310585327499e-10</v>
+        <v>1.828992957086939e-09</v>
       </c>
       <c r="EP3" t="n">
-        <v>2.079142413791146e-11</v>
+        <v>2.770795815010274e-10</v>
       </c>
       <c r="EQ3" t="n">
-        <v>3.49780382435938e-09</v>
+        <v>3.604355036657125e-09</v>
       </c>
       <c r="ER3" t="n">
-        <v>2.570614276997674e-10</v>
+        <v>1.903671442704535e-09</v>
       </c>
       <c r="ES3" t="n">
-        <v>3.709709872623534e-09</v>
+        <v>1.867085597240248e-09</v>
       </c>
       <c r="ET3" t="n">
-        <v>1.561689444429248e-09</v>
+        <v>2.988232772338506e-09</v>
       </c>
       <c r="EU3" t="n">
-        <v>4.602040970524968e-12</v>
+        <v>1.967699614358054e-10</v>
       </c>
       <c r="EV3" t="n">
-        <v>6.406626784638547e-09</v>
+        <v>1.765256607555443e-09</v>
       </c>
       <c r="EW3" t="n">
-        <v>1.287224549173516e-09</v>
+        <v>1.470017663152134e-09</v>
       </c>
       <c r="EX3" t="n">
-        <v>8.65500338065317e-10</v>
+        <v>2.094776796468523e-09</v>
       </c>
       <c r="EY3" t="n">
-        <v>2.275450716737737e-09</v>
+        <v>4.601661718339756e-09</v>
       </c>
       <c r="EZ3" t="n">
-        <v>2.434829227127011e-09</v>
+        <v>1.43310285860565e-09</v>
       </c>
       <c r="FA3" t="n">
-        <v>2.40222197689377e-09</v>
+        <v>6.352736670045545e-10</v>
       </c>
       <c r="FB3" t="n">
-        <v>8.753385793980328e-10</v>
+        <v>5.763047816742528e-10</v>
       </c>
       <c r="FC3" t="n">
-        <v>1.94269356157406e-09</v>
+        <v>2.133291321371189e-09</v>
       </c>
       <c r="FD3" t="n">
-        <v>5.648148615478021e-10</v>
+        <v>9.012275647979351e-11</v>
       </c>
       <c r="FE3" t="n">
-        <v>1.90024024293578e-10</v>
+        <v>9.639482545509281e-10</v>
       </c>
       <c r="FF3" t="n">
-        <v>2.578521174356752e-09</v>
+        <v>1.278806283089295e-09</v>
       </c>
       <c r="FG3" t="n">
-        <v>2.799332987635239e-09</v>
+        <v>2.16236029082495e-09</v>
       </c>
       <c r="FH3" t="n">
-        <v>4.453806212723066e-10</v>
+        <v>7.057524786802105e-09</v>
       </c>
       <c r="FI3" t="n">
-        <v>4.921782981170963e-09</v>
+        <v>1.18852261365987e-09</v>
       </c>
       <c r="FJ3" t="n">
-        <v>3.254055469525952e-09</v>
+        <v>3.65198338236894e-09</v>
       </c>
       <c r="FK3" t="n">
-        <v>1.529773419051139e-09</v>
+        <v>1.708584662640789e-10</v>
       </c>
       <c r="FL3" t="n">
-        <v>4.433030886819012e-10</v>
+        <v>3.757150424110733e-10</v>
       </c>
       <c r="FM3" t="n">
-        <v>2.032425117093339e-09</v>
+        <v>1.000689309194058e-09</v>
       </c>
       <c r="FN3" t="n">
-        <v>5.735176777932338e-09</v>
+        <v>2.567608126113896e-09</v>
       </c>
       <c r="FO3" t="n">
-        <v>1.333516352897135e-10</v>
+        <v>5.452634788127853e-09</v>
       </c>
       <c r="FP3" t="n">
-        <v>2.23224327910998e-09</v>
+        <v>3.648910062992172e-10</v>
       </c>
       <c r="FQ3" t="n">
-        <v>1.418214656823125e-09</v>
+        <v>7.90986476317812e-09</v>
       </c>
       <c r="FR3" t="n">
-        <v>1.879573829910441e-09</v>
+        <v>3.119706493137642e-09</v>
       </c>
       <c r="FS3" t="n">
-        <v>2.886549888003742e-10</v>
+        <v>1.853877273916282e-09</v>
       </c>
       <c r="FT3" t="n">
-        <v>1.185652465096609e-08</v>
+        <v>4.563848854388652e-09</v>
       </c>
       <c r="FU3" t="n">
-        <v>2.188473624542553e-09</v>
+        <v>2.461098436157272e-09</v>
       </c>
       <c r="FV3" t="n">
-        <v>1.9373933568545e-09</v>
+        <v>1.654299697229078e-09</v>
       </c>
       <c r="FW3" t="n">
-        <v>8.771303683374754e-10</v>
+        <v>5.617919462963528e-09</v>
       </c>
       <c r="FX3" t="n">
-        <v>5.970495209339788e-10</v>
+        <v>2.810853494406018e-10</v>
       </c>
       <c r="FY3" t="n">
-        <v>3.829414119138619e-09</v>
+        <v>4.767117256498921e-11</v>
       </c>
       <c r="FZ3" t="n">
-        <v>1.485451095462054e-09</v>
+        <v>3.145216975752874e-09</v>
       </c>
       <c r="GA3" t="n">
-        <v>1.491042844747881e-09</v>
+        <v>5.585492957038696e-09</v>
       </c>
       <c r="GB3" t="n">
-        <v>1.346407207947209e-09</v>
+        <v>2.046407931999283e-09</v>
       </c>
       <c r="GC3" t="n">
-        <v>4.653641472174286e-09</v>
+        <v>5.822927917620291e-09</v>
       </c>
       <c r="GD3" t="n">
-        <v>4.571355738391958e-09</v>
+        <v>7.284864711465389e-09</v>
       </c>
       <c r="GE3" t="n">
-        <v>6.229492477416443e-09</v>
+        <v>6.826198495346603e-10</v>
       </c>
       <c r="GF3" t="n">
-        <v>1.796018000987942e-09</v>
+        <v>1.003416461031748e-09</v>
       </c>
       <c r="GG3" t="n">
-        <v>3.422727434809758e-09</v>
+        <v>2.125141840281231e-09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0005771024734713137</v>
+        <v>1.641073765767942e-07</v>
       </c>
       <c r="B4" t="n">
-        <v>0.004974663723260164</v>
+        <v>3.151954160784953e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004089342837687582</v>
+        <v>1.591580939930282e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001239048084244132</v>
+        <v>8.986749548967055e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003769415779970586</v>
+        <v>1.833858505051467e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003316868329420686</v>
+        <v>5.192473054194124e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003632458974607289</v>
+        <v>2.993218686242471e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001318353693932295</v>
+        <v>5.954279913567007e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003994864819105715</v>
+        <v>4.120932430851099e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008084414293989539</v>
+        <v>7.110229489626363e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004669442307204008</v>
+        <v>2.401462779744179e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>7.879140321165323e-05</v>
+        <v>2.34151275435579e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001086859381757677</v>
+        <v>1.395012873217638e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004276010440662503</v>
+        <v>4.207792017041356e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002763615222647786</v>
+        <v>5.772827080363641e-06</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001277661940548569</v>
+        <v>2.035527018051653e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0004033671866636723</v>
+        <v>5.311258632900717e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0005520108970813453</v>
+        <v>8.477744017909572e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>7.795965211698785e-05</v>
+        <v>8.597156124778849e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0003713583282660693</v>
+        <v>3.578228415790363e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001088162389351055</v>
+        <v>7.05062348060892e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0004248151089996099</v>
+        <v>7.305435474336264e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0006534760468639433</v>
+        <v>2.606432190077612e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001467937545385212</v>
+        <v>6.089402404541033e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001620704424567521</v>
+        <v>5.205638444749638e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0007277175900526345</v>
+        <v>4.366068537819956e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0003984159848187119</v>
+        <v>3.66146394981115e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.055889439769089e-05</v>
+        <v>7.955262617542758e-07</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0001179402388515882</v>
+        <v>1.134658873525041e-07</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0001111245946958661</v>
+        <v>1.010905066323176e-06</v>
       </c>
       <c r="AE4" t="n">
-        <v>7.935341272968799e-05</v>
+        <v>1.238628101418726e-06</v>
       </c>
       <c r="AF4" t="n">
-        <v>4.822594928555191e-05</v>
+        <v>4.963052333550877e-07</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.000205260599614121</v>
+        <v>1.000518977889442e-06</v>
       </c>
       <c r="AH4" t="n">
-        <v>9.902739839162678e-05</v>
+        <v>3.311741920697386e-07</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.610272374819033e-05</v>
+        <v>1.955640527739888e-06</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.435754479141906e-05</v>
+        <v>3.065104010602226e-07</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0006725655402988195</v>
+        <v>1.059666260516678e-06</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0003315731592010707</v>
+        <v>5.603160957434739e-07</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.379309004638344e-05</v>
+        <v>7.688434493502427e-07</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0002375035546720028</v>
+        <v>8.780083362580626e-07</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.803532207617536e-05</v>
+        <v>3.257292178204807e-07</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0007166836876422167</v>
+        <v>4.685083183630923e-07</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0001352414983557537</v>
+        <v>6.0567657556021e-09</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0002576708211563528</v>
+        <v>7.804030133229389e-07</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0004856211016885936</v>
+        <v>2.888911581067077e-07</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0001316210982622579</v>
+        <v>3.721605139617168e-07</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002732326509431005</v>
+        <v>2.507649242033949e-06</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.000351382332155481</v>
+        <v>1.911333583848318e-06</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0003308120940346271</v>
+        <v>6.282100457610795e-07</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0003337915404699743</v>
+        <v>1.061972625393537e-06</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001671246718615294</v>
+        <v>2.822655460477108e-06</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0008872932521626353</v>
+        <v>7.998254858421205e-08</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0003338464593980461</v>
+        <v>6.120674811427307e-07</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0007943118689581752</v>
+        <v>3.161004258345201e-07</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0002694679133128375</v>
+        <v>2.530859717353451e-07</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001147042610682547</v>
+        <v>6.02935230631374e-08</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001047824276611209</v>
+        <v>4.967965878677205e-07</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0002398980723228306</v>
+        <v>1.00558622762037e-07</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0002781382645480335</v>
+        <v>2.087479742840515e-06</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0006595614831894636</v>
+        <v>2.352165040520049e-07</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.000154363558976911</v>
+        <v>2.708769102355291e-07</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0003942702314816415</v>
+        <v>4.623454969987506e-07</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0005307948449626565</v>
+        <v>4.597211855639216e-08</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0002238723973277956</v>
+        <v>3.153867567107227e-08</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0008835510816425085</v>
+        <v>1.004772116175445e-06</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0004779844894073904</v>
+        <v>1.028181912943182e-07</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.703420124016702e-06</v>
+        <v>3.916198920705938e-07</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0004994742339476943</v>
+        <v>1.222302188352842e-07</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.671621278859675e-05</v>
+        <v>7.344887080762419e-07</v>
       </c>
       <c r="BR4" t="n">
-        <v>6.274960469454527e-05</v>
+        <v>3.292281860467483e-07</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0002638435980770737</v>
+        <v>6.093866744549814e-08</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0001230862981174141</v>
+        <v>5.157933173904894e-07</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.273671245551668e-05</v>
+        <v>5.183650273465901e-07</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001780475256964564</v>
+        <v>1.41039436130086e-06</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0003191118885297328</v>
+        <v>7.024053729765001e-07</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0002452172338962555</v>
+        <v>6.015981739437848e-07</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0001181519837700762</v>
+        <v>1.514321184004075e-07</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0005854091141372919</v>
+        <v>1.981741888812394e-06</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.978133413009346e-05</v>
+        <v>9.489257877248747e-07</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0001009318220894784</v>
+        <v>1.935530917762662e-07</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0003697169304359704</v>
+        <v>5.351787990548473e-08</v>
       </c>
       <c r="CD4" t="n">
-        <v>8.856532804202288e-05</v>
+        <v>4.095652883506773e-08</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0008657994912937284</v>
+        <v>1.030107796395896e-06</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0003391310747247189</v>
+        <v>3.350600650264823e-07</v>
       </c>
       <c r="CG4" t="n">
-        <v>9.588690591044724e-05</v>
+        <v>8.64125340171995e-08</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0002285038935951889</v>
+        <v>3.926860756564565e-07</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0004347097419667989</v>
+        <v>1.07382027181302e-06</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0002886730362661183</v>
+        <v>4.112109763809713e-09</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0002495498047210276</v>
+        <v>2.004524759513515e-07</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0003276727511547506</v>
+        <v>1.062981880295411e-07</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001094976789318025</v>
+        <v>3.438713918058056e-07</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0004829751560464501</v>
+        <v>9.31391809899651e-07</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.465510649723001e-05</v>
+        <v>1.336912305305304e-06</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.001075496664270759</v>
+        <v>6.796336293746208e-08</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0004383531340863556</v>
+        <v>5.986468067931128e-07</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.001140284119173884</v>
+        <v>6.555084155479562e-07</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0008946896414272487</v>
+        <v>1.069097265826713e-06</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.000781742506660521</v>
+        <v>8.34318313991389e-07</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0002371762675466016</v>
+        <v>1.753299443407741e-07</v>
       </c>
       <c r="CV4" t="n">
-        <v>6.461502198362723e-05</v>
+        <v>3.171203388774302e-07</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0008512447820976377</v>
+        <v>9.969610346161062e-07</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0003773046482820064</v>
+        <v>5.225525683272281e-07</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0003199713537469506</v>
+        <v>1.693436786354141e-07</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0001913229934871197</v>
+        <v>2.750506666870933e-07</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0004694237723015249</v>
+        <v>1.189853946925723e-06</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0002740625932347029</v>
+        <v>2.258306253111186e-08</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.0005163231980986893</v>
+        <v>2.015220275097818e-07</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0002475809014867991</v>
+        <v>1.777947318259976e-07</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0003377607208676636</v>
+        <v>2.554824618528073e-07</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.001024027820676565</v>
+        <v>2.58042496170674e-06</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.000168309808941558</v>
+        <v>9.459457714910968e-07</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0008175015682354569</v>
+        <v>4.312208261580963e-07</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001345511060208082</v>
+        <v>1.829843654377328e-07</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0007523530512116849</v>
+        <v>1.371781991110765e-06</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0002425070997560397</v>
+        <v>2.783702512942909e-08</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0007787880022078753</v>
+        <v>1.49319362208189e-06</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001004621502943337</v>
+        <v>1.083961592485139e-06</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.0002388607827015221</v>
+        <v>4.681976975007274e-07</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.000470401719212532</v>
+        <v>1.436711727365036e-06</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0003327695885673165</v>
+        <v>2.193359875946044e-07</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0003788528265431523</v>
+        <v>8.978787491287221e-07</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0003619967319536954</v>
+        <v>1.969268339507835e-07</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0004383494087960571</v>
+        <v>1.365327989333309e-06</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0004589098098222166</v>
+        <v>5.201890189709957e-07</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0002353305753786117</v>
+        <v>7.750613804091699e-07</v>
       </c>
       <c r="DV4" t="n">
-        <v>6.853895320091397e-05</v>
+        <v>1.236408024851698e-07</v>
       </c>
       <c r="DW4" t="n">
-        <v>3.336512600071728e-05</v>
+        <v>4.142243881233298e-09</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0006094630225561559</v>
+        <v>3.635551593106356e-07</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0002918093232437968</v>
+        <v>1.878575176306185e-06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.000317262951284647</v>
+        <v>3.226071498829697e-08</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0004248965997248888</v>
+        <v>6.337206173157028e-07</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0004657743265852332</v>
+        <v>3.471803893262404e-07</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.000134582631289959</v>
+        <v>6.32575051895401e-07</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0001698965788818896</v>
+        <v>7.516333084822691e-07</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0008021392859518528</v>
+        <v>1.927382072608452e-06</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0005380400107242167</v>
+        <v>1.483419396208774e-07</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0008031110046431422</v>
+        <v>2.963845133763243e-07</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0004963247338309884</v>
+        <v>7.134218549254001e-08</v>
       </c>
       <c r="EI4" t="n">
-        <v>3.465386544121429e-05</v>
+        <v>1.717192077421714e-07</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0001187793459394015</v>
+        <v>7.500067908949859e-07</v>
       </c>
       <c r="EK4" t="n">
-        <v>3.214291064068675e-05</v>
+        <v>4.119216043818597e-07</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0002662402403075248</v>
+        <v>9.174107873377579e-08</v>
       </c>
       <c r="EM4" t="n">
-        <v>3.411633224459365e-05</v>
+        <v>2.238571994439553e-07</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0001650984777370468</v>
+        <v>5.310319579621137e-07</v>
       </c>
       <c r="EO4" t="n">
-        <v>8.594688551966101e-06</v>
+        <v>2.899298578995513e-09</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0005969742778688669</v>
+        <v>5.253154427009576e-07</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0001184266875497997</v>
+        <v>7.795669034749153e-07</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0002579508582130075</v>
+        <v>6.167495030240389e-07</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0004791374667547643</v>
+        <v>1.278374838875607e-06</v>
       </c>
       <c r="ET4" t="n">
-        <v>6.464761827373877e-05</v>
+        <v>7.815432923052867e-08</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0008785936515778303</v>
+        <v>8.433873688318272e-08</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.001216894015669823</v>
+        <v>9.580986670698621e-09</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.000149600047734566</v>
+        <v>4.858251259065582e-07</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0001543554535601288</v>
+        <v>2.330040445031045e-07</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0007986095151863992</v>
+        <v>1.071230371962884e-06</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0002551430370658636</v>
+        <v>3.76937890678164e-07</v>
       </c>
       <c r="FA4" t="n">
-        <v>7.379001908702776e-05</v>
+        <v>2.287809195422597e-07</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.000158086812007241</v>
+        <v>3.945587820908258e-07</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0003923579934053123</v>
+        <v>1.162372655016952e-06</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0004376435535959899</v>
+        <v>2.335023623345478e-07</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0003857370174955577</v>
+        <v>1.697194704775029e-07</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0003787712776102126</v>
+        <v>4.266923383511312e-07</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0002479639078956097</v>
+        <v>6.249807427138876e-08</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0002990103384945542</v>
+        <v>9.276702712668339e-07</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0002573147648945451</v>
+        <v>1.282352513953811e-06</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0006636810721829534</v>
+        <v>4.91887249154388e-07</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0003221658698748797</v>
+        <v>4.006682274848572e-08</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0003309314779471606</v>
+        <v>1.067485754902009e-06</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0002475739747751504</v>
+        <v>1.585766540301847e-07</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0003886115446221083</v>
+        <v>1.263386707250902e-06</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0001210597838507965</v>
+        <v>1.550009187667456e-06</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0004296586848795414</v>
+        <v>1.295705146731052e-06</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0003617112815845758</v>
+        <v>2.36476671489072e-06</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.000688987725879997</v>
+        <v>3.464080009507597e-07</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0002259055327158421</v>
+        <v>1.184966777145746e-06</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0002013542398344725</v>
+        <v>1.428151790605625e-06</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0005394534091465175</v>
+        <v>5.736926596000558e-07</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0001579647941980511</v>
+        <v>3.627488354140951e-07</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0001732573146000504</v>
+        <v>2.743294317042455e-06</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0002756107714958489</v>
+        <v>4.679488370129548e-07</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.0005984271410852671</v>
+        <v>4.097321948393073e-07</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0004132075991947204</v>
+        <v>1.166776044669859e-07</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0004130032612010837</v>
+        <v>1.436817456124118e-06</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0001093890168704093</v>
+        <v>2.00236840441903e-07</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.000388205808121711</v>
+        <v>1.718384396554029e-06</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0004434413567651063</v>
+        <v>1.188289616038674e-06</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.0007671568891964853</v>
+        <v>3.890393429628602e-07</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0003015713882632554</v>
+        <v>9.832800742515246e-07</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0002804672403726727</v>
+        <v>1.675176974913484e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.000764468451961875</v>
+        <v>2.93024743358572e-10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01806899346411228</v>
+        <v>1.872793919943661e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00093704869505018</v>
+        <v>7.751532193900346e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005316698923707008</v>
+        <v>1.087090861773277e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006376648787409067</v>
+        <v>1.048873210507395e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01174366753548384</v>
+        <v>9.011380530665747e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002048744820058346</v>
+        <v>2.091461448472387e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003120846580713987</v>
+        <v>3.309536811268998e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001218361780047417</v>
+        <v>1.031945195961725e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002362097846344113</v>
+        <v>9.385436872122455e-12</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01915952377021313</v>
+        <v>4.590649804736557e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003513519186526537</v>
+        <v>5.512887368830377e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003765707369893789</v>
+        <v>6.018409659525048e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002832596888765693</v>
+        <v>4.407518794380394e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01070560608059168</v>
+        <v>2.502281937211137e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002097982913255692</v>
+        <v>7.274799651568742e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001015484565868974</v>
+        <v>1.967554341675282e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0005205097841098905</v>
+        <v>1.821158113202159e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000610179384239018</v>
+        <v>2.130874143801975e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00180720875505358</v>
+        <v>9.865230854444462e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001357704168185592</v>
+        <v>1.621637713000723e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002427314640954137</v>
+        <v>5.470980335431364e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001905281678773463</v>
+        <v>1.507832858571589e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0009358823299407959</v>
+        <v>5.716001005851012e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0003622365475166589</v>
+        <v>2.511901797674909e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001278931740671396</v>
+        <v>1.962408013866934e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001350188511423767</v>
+        <v>8.549388974543604e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.001150052063167095</v>
+        <v>1.998738285990953e-09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.001039483584463596</v>
+        <v>3.820837535251087e-10</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.002512376522645354</v>
+        <v>1.975593910685802e-09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001803095219656825</v>
+        <v>4.456486013548755e-10</v>
       </c>
       <c r="AF5" t="n">
-        <v>7.558934157714248e-05</v>
+        <v>1.340879296485298e-09</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001415615435689688</v>
+        <v>4.698689215487661e-10</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.000355861964635551</v>
+        <v>1.346342259900268e-09</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.001090591074898839</v>
+        <v>8.115886851456366e-10</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001437325496226549</v>
+        <v>6.159041610054317e-10</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.001878150273114443</v>
+        <v>1.50315215829977e-09</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.002560976427048445</v>
+        <v>5.023002569437551e-10</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.002294081496074796</v>
+        <v>7.650619027188554e-10</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.757120278663933e-05</v>
+        <v>2.07802941520896e-11</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0005897164810448885</v>
+        <v>2.157143574876841e-09</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.00134320673532784</v>
+        <v>3.12493808607428e-10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0003548663516994566</v>
+        <v>8.253552286063837e-10</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0007106041302904487</v>
+        <v>3.850293861518139e-09</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.00104380608536303</v>
+        <v>1.630138524166824e-10</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.001073335530236363</v>
+        <v>1.318326336985365e-09</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0113259581848979</v>
+        <v>3.200715026352441e-09</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.003105471841990948</v>
+        <v>1.299757634853904e-09</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0006774658686481416</v>
+        <v>4.196147873614109e-10</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0009494919213466346</v>
+        <v>2.263309539785041e-09</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.005627232138067484</v>
+        <v>2.440479152099329e-09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.001679497538134456</v>
+        <v>8.453048261358731e-10</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0001355764688923955</v>
+        <v>5.087115728663605e-10</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0009463521419093013</v>
+        <v>1.139742675237976e-10</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0008261841721832752</v>
+        <v>4.228313699172759e-09</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.003890244290232658</v>
+        <v>2.714918068136285e-09</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.003256524447351694</v>
+        <v>2.401337462210051e-11</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0002775084285531193</v>
+        <v>1.538107641252395e-09</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.005210649687796831</v>
+        <v>3.572200757417932e-09</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.005717092659324408</v>
+        <v>2.032409240904087e-10</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001241746358573437</v>
+        <v>3.041800700209762e-10</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0003916898858733475</v>
+        <v>4.960780120022434e-10</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0006222397787496448</v>
+        <v>1.91528282122988e-09</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.002491889288648963</v>
+        <v>2.997294079598589e-10</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.002336620818823576</v>
+        <v>8.350057312256354e-10</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0005702084163203835</v>
+        <v>7.229212228843096e-10</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0001993255427805707</v>
+        <v>1.351633804880237e-09</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.001826070831157267</v>
+        <v>9.022081970400109e-10</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0005947010358795524</v>
+        <v>5.585108486805268e-10</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0009443324524909258</v>
+        <v>3.804924153527622e-10</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.001008659484796226</v>
+        <v>1.017958425886256e-10</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0004204838769510388</v>
+        <v>2.004602928096233e-09</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0005814715987071395</v>
+        <v>2.21019358370711e-09</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.006888566073030233</v>
+        <v>2.793804965151025e-09</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0007190695032477379</v>
+        <v>1.159733753475223e-09</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.001691934419795871</v>
+        <v>1.556568429705862e-09</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0001598598319105804</v>
+        <v>7.188050710205118e-10</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.001032817643135786</v>
+        <v>1.415580874741806e-09</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0005699283210560679</v>
+        <v>1.302114194245974e-09</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0001641449925955385</v>
+        <v>4.959320731856565e-10</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.00107300968375057</v>
+        <v>8.728136269287035e-11</v>
       </c>
       <c r="CD5" t="n">
-        <v>9.663710079621524e-05</v>
+        <v>2.10993694738093e-10</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.003119596047326922</v>
+        <v>2.328050807687276e-10</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0004091945302207023</v>
+        <v>4.118140828346384e-10</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.00108615995850414</v>
+        <v>7.417083613958653e-11</v>
       </c>
       <c r="CH5" t="n">
-        <v>9.19846206670627e-05</v>
+        <v>3.745526389042908e-10</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.002016023267060518</v>
+        <v>5.022607330040785e-10</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.001805417239665985</v>
+        <v>2.252039943417827e-10</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.000280327774817124</v>
+        <v>5.59880808381763e-10</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0004251926438882947</v>
+        <v>1.312674524633906e-09</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.004144058562815189</v>
+        <v>6.741477931448969e-10</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.001598765840753913</v>
+        <v>3.221154898369605e-09</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.000117470946861431</v>
+        <v>6.75820177598041e-10</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.002375355456024408</v>
+        <v>1.247563830020226e-09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.001330534345470369</v>
+        <v>1.915047453948659e-09</v>
       </c>
       <c r="CR5" t="n">
-        <v>5.454419806483202e-05</v>
+        <v>2.085870365320375e-09</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.003544246777892113</v>
+        <v>3.087790911848742e-09</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.003356714965775609</v>
+        <v>2.177520663781962e-10</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0009975009597837925</v>
+        <v>1.611875188878287e-09</v>
       </c>
       <c r="CV5" t="n">
-        <v>7.210395415313542e-05</v>
+        <v>1.603333577016031e-10</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.002897170837968588</v>
+        <v>4.251656526843561e-10</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0002198495203629136</v>
+        <v>7.463272222452133e-10</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.001579901669174433</v>
+        <v>3.495490008553759e-10</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0002221314935013652</v>
+        <v>4.204495085424753e-10</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.002137304982170463</v>
+        <v>8.787338912075171e-11</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.001723106019198895</v>
+        <v>5.131647884404344e-11</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0005554380477406085</v>
+        <v>2.329013926161139e-10</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0001573315385030583</v>
+        <v>1.070099564515203e-09</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.001539138378575444</v>
+        <v>5.15235742959419e-10</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.003869823412969708</v>
+        <v>2.692801537307332e-09</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0006068335496820509</v>
+        <v>3.259375214170745e-09</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.002803790383040905</v>
+        <v>9.305117232294435e-10</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.004814127460122108</v>
+        <v>2.590048175932225e-09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001681815017946064</v>
+        <v>9.566120118265076e-10</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.001333677559159696</v>
+        <v>1.247314029839686e-09</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0002639006997924298</v>
+        <v>8.094810932668395e-10</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.002562227658927441</v>
+        <v>1.438617225346661e-09</v>
       </c>
       <c r="DN5" t="n">
-        <v>2.438219962641597e-05</v>
+        <v>8.151088692898156e-10</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0005185230984352529</v>
+        <v>4.06545713760309e-10</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001731055090203881</v>
+        <v>5.347674525424395e-10</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.001918542780913413</v>
+        <v>1.906929891770659e-10</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.001153097720816731</v>
+        <v>3.999365283391398e-10</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.001604973222129047</v>
+        <v>7.268750601419072e-10</v>
       </c>
       <c r="DT5" t="n">
-        <v>9.144918294623494e-05</v>
+        <v>5.94036819734356e-10</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0006108140805736184</v>
+        <v>1.692033180233921e-10</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0005805273540318012</v>
+        <v>1.923619263877185e-09</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.001021307893097401</v>
+        <v>5.307621009364993e-11</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.002146414946764708</v>
+        <v>1.370093372088377e-09</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0009892666712403297</v>
+        <v>1.440611629988098e-09</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0007347101345658302</v>
+        <v>5.347022269397428e-10</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001136300386860967</v>
+        <v>4.097230610344837e-10</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.001640645554289222</v>
+        <v>7.158921233596516e-10</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.001594779663719237</v>
+        <v>4.188288382778182e-09</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.002045923611149192</v>
+        <v>6.018248122074965e-10</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0006145373918116093</v>
+        <v>1.113328762514243e-09</v>
       </c>
       <c r="EF5" t="n">
-        <v>9.09301161300391e-05</v>
+        <v>1.030021762327138e-10</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.003345363074913621</v>
+        <v>1.412833072755859e-09</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0004090658621862531</v>
+        <v>6.761592674653372e-11</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.001108984230086207</v>
+        <v>4.659187480271498e-10</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0002960688434541225</v>
+        <v>5.609985809229556e-10</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.001794645795598626</v>
+        <v>7.133264118275306e-11</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.00158991850912571</v>
+        <v>1.393237525348923e-09</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.001040622708387673</v>
+        <v>2.729121095779163e-10</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.000543212634511292</v>
+        <v>2.507304142085331e-09</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0001418631873093545</v>
+        <v>4.189847357949361e-10</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.002384066116064787</v>
+        <v>6.303912947203116e-10</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0001845589140430093</v>
+        <v>3.252272895437613e-10</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0002386429405305535</v>
+        <v>3.19020976302653e-10</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0008263649069704115</v>
+        <v>4.878193959889643e-10</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.001578424707986414</v>
+        <v>1.758236445326133e-09</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.001638583955354989</v>
+        <v>1.411022187980393e-09</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.002127572661265731</v>
+        <v>1.010727834760416e-09</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001355582848191261</v>
+        <v>9.312800530736354e-11</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0003119652392342687</v>
+        <v>9.847535981100108e-11</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.002778553869575262</v>
+        <v>1.69629005286609e-10</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0002322797372471541</v>
+        <v>3.677109450261895e-10</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0009999503381550312</v>
+        <v>4.036607159640937e-10</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0005356902256608009</v>
+        <v>6.578275701940584e-10</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.002199431415647268</v>
+        <v>3.038508888941749e-10</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.001665772637352347</v>
+        <v>2.357848638556703e-10</v>
       </c>
       <c r="FE5" t="n">
-        <v>9.136101289186627e-05</v>
+        <v>9.791608496234616e-11</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0003677012282423675</v>
+        <v>1.093560908493885e-09</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0002044881111942232</v>
+        <v>3.160456896189601e-10</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001368745230138302</v>
+        <v>1.911414138078271e-09</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0006900145672261715</v>
+        <v>3.422655214802006e-10</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.003148133400827646</v>
+        <v>1.414160233359496e-09</v>
       </c>
       <c r="FK5" t="n">
-        <v>2.908476017182693e-05</v>
+        <v>3.478819177171744e-10</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.001004987629130483</v>
+        <v>1.67808344997411e-09</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0002869214513339102</v>
+        <v>2.033667456657895e-09</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0003884472243953496</v>
+        <v>4.655700824862663e-10</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0003947429649997503</v>
+        <v>2.621081574005757e-09</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001440352760255337</v>
+        <v>3.454322605733751e-09</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.003150528995320201</v>
+        <v>4.767695127583238e-10</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.001188452122732997</v>
+        <v>1.860126275232687e-09</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.001372435828670859</v>
+        <v>3.220327782216259e-09</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.00205652741715312</v>
+        <v>3.655908464850199e-09</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0003830263740383089</v>
+        <v>1.833977691934052e-10</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.001436226884834468</v>
+        <v>2.346518090945438e-09</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.002730839420109987</v>
+        <v>5.108522938002125e-09</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0004179435491096228</v>
+        <v>2.691062095383501e-10</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.002164729638025165</v>
+        <v>3.176644780555904e-10</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0002292276185471565</v>
+        <v>7.050302563982314e-10</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0004488844133447856</v>
+        <v>2.054794334682697e-09</v>
       </c>
       <c r="GB5" t="n">
-        <v>2.057247911579907e-05</v>
+        <v>1.683821970743793e-10</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.001029119128361344</v>
+        <v>4.493262428795219e-10</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0002620379964355379</v>
+        <v>1.756604584013388e-11</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.002903996268287301</v>
+        <v>1.204119581821317e-09</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.001519991550594568</v>
+        <v>1.689148598771339e-09</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.001046576071530581</v>
+        <v>3.656830394049848e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6.113253675721353e-06</v>
+        <v>3.701680952872266e-07</v>
       </c>
       <c r="B6" t="n">
-        <v>8.693249401403591e-05</v>
+        <v>4.877358151134104e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>7.582895705127157e-06</v>
+        <v>2.769505726973875e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.920752012869343e-05</v>
+        <v>3.071856326641864e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.467184301873203e-05</v>
+        <v>3.266695216552762e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.352016624878161e-05</v>
+        <v>5.730534212489147e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>8.686994988238439e-06</v>
+        <v>9.492737262917217e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>8.439671546511818e-06</v>
+        <v>1.745919462337042e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.330287422111724e-06</v>
+        <v>2.653345632097626e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.422006971552037e-05</v>
+        <v>7.905752852366277e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.849703640909865e-05</v>
+        <v>4.890797299594851e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>3.010917907886324e-06</v>
+        <v>3.425513568799943e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>2.989869972225279e-05</v>
+        <v>5.100634552945849e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>2.269712240376975e-05</v>
+        <v>2.71130943474418e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>2.848147414624691e-05</v>
+        <v>5.43919350093347e-06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.218749093823135e-05</v>
+        <v>7.267107093866798e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.68545192941383e-06</v>
+        <v>8.644681201985804e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.095101424652967e-06</v>
+        <v>2.157070611019662e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>4.732526122097624e-06</v>
+        <v>5.26251710653014e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.179684204544174e-05</v>
+        <v>3.108794430772832e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>5.189682724449085e-06</v>
+        <v>7.127516710170312e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>4.540174813882913e-06</v>
+        <v>8.59502392813738e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>3.454770876487601e-06</v>
+        <v>1.065761352947447e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.165019148174906e-05</v>
+        <v>9.116455998992024e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.014343853166793e-06</v>
+        <v>2.974664710109209e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.50614432641305e-05</v>
+        <v>2.936677674370003e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.124100162996911e-05</v>
+        <v>4.477601578400936e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.473206667578779e-06</v>
+        <v>1.616504619050829e-07</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.407351404253859e-06</v>
+        <v>4.952299832439166e-07</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.032137313624844e-07</v>
+        <v>8.356556691069272e-07</v>
       </c>
       <c r="AE6" t="n">
-        <v>6.136401680123527e-07</v>
+        <v>4.43806470684649e-07</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.430984846403589e-07</v>
+        <v>3.90256218452123e-07</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.359986072202446e-06</v>
+        <v>2.553262220317265e-06</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.409335244621616e-06</v>
+        <v>1.923890522448346e-07</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.939520982181421e-06</v>
+        <v>2.519087956898147e-06</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.080784952340764e-06</v>
+        <v>3.599175215640571e-07</v>
       </c>
       <c r="AK6" t="n">
-        <v>6.777444468752947e-06</v>
+        <v>6.415824032046658e-07</v>
       </c>
       <c r="AL6" t="n">
-        <v>9.488689101999626e-06</v>
+        <v>1.406678279636253e-06</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.235373131043161e-06</v>
+        <v>6.941388619452482e-07</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.434200491232332e-06</v>
+        <v>8.276361995740444e-07</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.730968147574458e-06</v>
+        <v>3.473794265573815e-07</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.380164576403331e-06</v>
+        <v>4.740300312278123e-07</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.647217555335374e-07</v>
+        <v>2.77969718354143e-08</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.472766477192636e-07</v>
+        <v>9.609044582248316e-07</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.692820079479134e-06</v>
+        <v>3.648907522801892e-07</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.995707281021168e-06</v>
+        <v>4.457949671632377e-07</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.391734521253966e-05</v>
+        <v>4.093103143532062e-06</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.4958969738218e-06</v>
+        <v>1.791816430340987e-06</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.136140417656861e-05</v>
+        <v>1.914732592922519e-06</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.022938578098547e-06</v>
+        <v>3.123361693724291e-06</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.795093890512362e-06</v>
+        <v>2.562031113484409e-06</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.315708105830709e-06</v>
+        <v>2.011499589116283e-08</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.154265636519995e-07</v>
+        <v>6.41724000161048e-07</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.429349958925741e-05</v>
+        <v>6.929190590199141e-07</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.056647074117791e-06</v>
+        <v>4.879358357356978e-07</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.101069367199671e-05</v>
+        <v>8.878232620190829e-07</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.044915163423866e-05</v>
+        <v>1.830376049838378e-06</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.660124664544128e-06</v>
+        <v>1.015733914755401e-06</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.355809217784554e-05</v>
+        <v>1.889036639113328e-06</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.670841351777199e-06</v>
+        <v>1.739361323416233e-06</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.169108145404607e-05</v>
+        <v>1.642469698026616e-07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>6.45605268800864e-06</v>
+        <v>6.65525703880121e-07</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.678756345630973e-07</v>
+        <v>3.425283523483813e-08</v>
       </c>
       <c r="BL6" t="n">
-        <v>4.081396127730841e-06</v>
+        <v>1.261321074252919e-07</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.948376489570364e-06</v>
+        <v>1.411624452885007e-06</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.32980394482729e-05</v>
+        <v>5.756379550803103e-07</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.475492914934875e-06</v>
+        <v>2.252230899557617e-07</v>
       </c>
       <c r="BP6" t="n">
-        <v>8.455069291812833e-06</v>
+        <v>3.76334071461315e-07</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.578036166298261e-07</v>
+        <v>1.094088929676218e-06</v>
       </c>
       <c r="BR6" t="n">
-        <v>3.561674702723394e-06</v>
+        <v>1.150492380475043e-06</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.273965719723492e-06</v>
+        <v>2.764008684152941e-07</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.763462468166836e-06</v>
+        <v>3.739474152553157e-07</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.572630935697816e-06</v>
+        <v>7.86211785452906e-07</v>
       </c>
       <c r="BV6" t="n">
-        <v>3.026959348062519e-05</v>
+        <v>2.927122750406852e-06</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.770499905745964e-06</v>
+        <v>1.341949655397912e-06</v>
       </c>
       <c r="BX6" t="n">
-        <v>8.66755817696685e-06</v>
+        <v>2.413489028185722e-06</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.958564098458737e-06</v>
+        <v>1.106247509596869e-06</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.774251925075077e-06</v>
+        <v>1.717227632980212e-06</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.209482995065628e-06</v>
+        <v>9.251834853785113e-07</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.154448450004566e-06</v>
+        <v>3.721257613165108e-08</v>
       </c>
       <c r="CC6" t="n">
-        <v>8.77015645528445e-06</v>
+        <v>2.322201879678687e-07</v>
       </c>
       <c r="CD6" t="n">
-        <v>1.07803714399779e-07</v>
+        <v>4.322970994508069e-07</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.435864851373481e-05</v>
+        <v>1.566168521094369e-06</v>
       </c>
       <c r="CF6" t="n">
-        <v>8.049655662034638e-06</v>
+        <v>5.714753115171334e-07</v>
       </c>
       <c r="CG6" t="n">
-        <v>1.208805429087079e-06</v>
+        <v>8.752684266255528e-07</v>
       </c>
       <c r="CH6" t="n">
-        <v>2.07018183573382e-06</v>
+        <v>1.837026388784579e-07</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.00929275706585e-06</v>
+        <v>1.281537606701022e-06</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.760202278295765e-06</v>
+        <v>2.166934223168937e-07</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.25800329442427e-06</v>
+        <v>4.658423620185204e-07</v>
       </c>
       <c r="CL6" t="n">
-        <v>4.654418262362015e-06</v>
+        <v>4.530685941972479e-07</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.185607809224166e-05</v>
+        <v>1.127197265304858e-06</v>
       </c>
       <c r="CN6" t="n">
-        <v>7.850158908695448e-06</v>
+        <v>5.718781608265999e-07</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.294043613597751e-06</v>
+        <v>2.454418336128583e-06</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.769747177604586e-05</v>
+        <v>9.6949747785402e-07</v>
       </c>
       <c r="CQ6" t="n">
-        <v>9.860893442237284e-06</v>
+        <v>3.068681166951137e-07</v>
       </c>
       <c r="CR6" t="n">
-        <v>8.083050488494337e-06</v>
+        <v>8.320116506865816e-08</v>
       </c>
       <c r="CS6" t="n">
-        <v>1.238621734955814e-05</v>
+        <v>3.094437488471158e-07</v>
       </c>
       <c r="CT6" t="n">
-        <v>9.030125511344522e-06</v>
+        <v>6.114661346146022e-07</v>
       </c>
       <c r="CU6" t="n">
-        <v>3.379968575245584e-06</v>
+        <v>3.524649514474731e-07</v>
       </c>
       <c r="CV6" t="n">
-        <v>5.141941983310971e-08</v>
+        <v>5.858044005435659e-07</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.308512946707197e-05</v>
+        <v>1.444000531591882e-06</v>
       </c>
       <c r="CX6" t="n">
-        <v>8.761982826399617e-06</v>
+        <v>8.406369715885376e-07</v>
       </c>
       <c r="CY6" t="n">
-        <v>5.408630840975093e-06</v>
+        <v>9.189546972265816e-07</v>
       </c>
       <c r="CZ6" t="n">
-        <v>4.155905571678886e-06</v>
+        <v>3.61021221806368e-07</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.522586330793274e-06</v>
+        <v>1.346935505353031e-06</v>
       </c>
       <c r="DB6" t="n">
-        <v>2.92565482595819e-06</v>
+        <v>1.546282675235489e-07</v>
       </c>
       <c r="DC6" t="n">
-        <v>3.022129476448754e-06</v>
+        <v>4.860819444729714e-07</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.040746378246695e-06</v>
+        <v>3.407033375424362e-07</v>
       </c>
       <c r="DE6" t="n">
-        <v>8.534728294762317e-06</v>
+        <v>8.402960247622104e-07</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.093062451218429e-06</v>
+        <v>1.991243607335491e-06</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.231270744028734e-06</v>
+        <v>8.812115765977069e-07</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.236285061168019e-05</v>
+        <v>1.266846538783284e-06</v>
       </c>
       <c r="DI6" t="n">
-        <v>3.260513722125324e-06</v>
+        <v>7.966080062260517e-08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>9.483455869485624e-06</v>
+        <v>2.572229277575389e-06</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.463239863776835e-06</v>
+        <v>3.257432297232299e-07</v>
       </c>
       <c r="DL6" t="n">
-        <v>2.376174506935058e-06</v>
+        <v>1.754153117872193e-06</v>
       </c>
       <c r="DM6" t="n">
-        <v>6.314841357379919e-06</v>
+        <v>3.314148671051953e-07</v>
       </c>
       <c r="DN6" t="n">
-        <v>3.543874527167645e-07</v>
+        <v>1.16466208055499e-06</v>
       </c>
       <c r="DO6" t="n">
-        <v>4.775381512445165e-08</v>
+        <v>7.711448688496603e-07</v>
       </c>
       <c r="DP6" t="n">
-        <v>1.110521407099441e-05</v>
+        <v>8.645612297186744e-07</v>
       </c>
       <c r="DQ6" t="n">
-        <v>6.748800387867959e-06</v>
+        <v>1.052934024414753e-07</v>
       </c>
       <c r="DR6" t="n">
-        <v>3.858843228954356e-06</v>
+        <v>2.194543355926726e-07</v>
       </c>
       <c r="DS6" t="n">
-        <v>2.073268206004286e-06</v>
+        <v>2.645560641667544e-07</v>
       </c>
       <c r="DT6" t="n">
-        <v>8.111765964713413e-06</v>
+        <v>2.766926456843066e-07</v>
       </c>
       <c r="DU6" t="n">
-        <v>3.335896508360747e-06</v>
+        <v>8.705952723175869e-07</v>
       </c>
       <c r="DV6" t="n">
-        <v>3.088839775955421e-06</v>
+        <v>4.098784529560362e-07</v>
       </c>
       <c r="DW6" t="n">
-        <v>1.582184950166265e-06</v>
+        <v>4.884913664682244e-07</v>
       </c>
       <c r="DX6" t="n">
-        <v>1.208305729960557e-05</v>
+        <v>7.110268995802471e-08</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.649246188317193e-06</v>
+        <v>2.27782493311679e-06</v>
       </c>
       <c r="DZ6" t="n">
-        <v>9.246089121006662e-07</v>
+        <v>1.376333329972113e-06</v>
       </c>
       <c r="EA6" t="n">
-        <v>8.246416655310895e-06</v>
+        <v>5.215958935878007e-07</v>
       </c>
       <c r="EB6" t="n">
-        <v>7.746308256173506e-06</v>
+        <v>7.123058480829059e-07</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.152536578454601e-07</v>
+        <v>2.356976267492428e-07</v>
       </c>
       <c r="ED6" t="n">
-        <v>1.063948161572625e-06</v>
+        <v>9.790451258595567e-07</v>
       </c>
       <c r="EE6" t="n">
-        <v>1.929579411807936e-06</v>
+        <v>2.155928541469621e-06</v>
       </c>
       <c r="EF6" t="n">
-        <v>3.51608809978643e-06</v>
+        <v>1.005388980956923e-06</v>
       </c>
       <c r="EG6" t="n">
-        <v>1.345010605291463e-05</v>
+        <v>5.33243223799218e-07</v>
       </c>
       <c r="EH6" t="n">
-        <v>6.89311536916648e-06</v>
+        <v>8.16817930626712e-07</v>
       </c>
       <c r="EI6" t="n">
-        <v>1.854676838775049e-06</v>
+        <v>3.04994330235786e-07</v>
       </c>
       <c r="EJ6" t="n">
-        <v>1.633544115975383e-06</v>
+        <v>1.055862526300189e-07</v>
       </c>
       <c r="EK6" t="n">
-        <v>1.630574161026743e-06</v>
+        <v>8.258912771452742e-07</v>
       </c>
       <c r="EL6" t="n">
-        <v>5.095716460346011e-06</v>
+        <v>1.378736413926163e-07</v>
       </c>
       <c r="EM6" t="n">
-        <v>1.408392108714906e-06</v>
+        <v>2.558467997459957e-07</v>
       </c>
       <c r="EN6" t="n">
-        <v>2.860638915080926e-06</v>
+        <v>3.421669703129737e-07</v>
       </c>
       <c r="EO6" t="n">
-        <v>3.013110472238623e-07</v>
+        <v>3.744901562185987e-07</v>
       </c>
       <c r="EP6" t="n">
-        <v>5.702558610209962e-06</v>
+        <v>9.225400390278082e-07</v>
       </c>
       <c r="EQ6" t="n">
-        <v>8.128507033688948e-06</v>
+        <v>7.321583552766242e-07</v>
       </c>
       <c r="ER6" t="n">
-        <v>5.667819095833693e-06</v>
+        <v>2.205388227594085e-08</v>
       </c>
       <c r="ES6" t="n">
-        <v>6.400228357961169e-06</v>
+        <v>8.222425549320178e-07</v>
       </c>
       <c r="ET6" t="n">
-        <v>8.048666131799109e-06</v>
+        <v>5.12011865794193e-07</v>
       </c>
       <c r="EU6" t="n">
-        <v>1.299936411669478e-05</v>
+        <v>1.13355689279615e-07</v>
       </c>
       <c r="EV6" t="n">
-        <v>1.598442759132013e-05</v>
+        <v>5.08593700487836e-07</v>
       </c>
       <c r="EW6" t="n">
-        <v>2.196539981014212e-06</v>
+        <v>7.353129376497236e-07</v>
       </c>
       <c r="EX6" t="n">
-        <v>2.490789029252483e-06</v>
+        <v>5.405051410889428e-07</v>
       </c>
       <c r="EY6" t="n">
-        <v>1.314667133556213e-05</v>
+        <v>1.70714633895841e-06</v>
       </c>
       <c r="EZ6" t="n">
-        <v>6.83214648233843e-06</v>
+        <v>5.140298071637517e-07</v>
       </c>
       <c r="FA6" t="n">
-        <v>2.971282356156735e-06</v>
+        <v>1.186320105261984e-06</v>
       </c>
       <c r="FB6" t="n">
-        <v>2.088617065965082e-06</v>
+        <v>9.921121346678774e-08</v>
       </c>
       <c r="FC6" t="n">
-        <v>2.007370312639978e-06</v>
+        <v>1.086957126972266e-06</v>
       </c>
       <c r="FD6" t="n">
-        <v>5.370055532694096e-06</v>
+        <v>3.078810664192133e-07</v>
       </c>
       <c r="FE6" t="n">
-        <v>9.967177447833819e-07</v>
+        <v>4.312468320222251e-07</v>
       </c>
       <c r="FF6" t="n">
-        <v>5.113790393806994e-06</v>
+        <v>2.112249930519283e-09</v>
       </c>
       <c r="FG6" t="n">
-        <v>2.543782784414361e-06</v>
+        <v>1.513680842890608e-07</v>
       </c>
       <c r="FH6" t="n">
-        <v>1.721175863167446e-06</v>
+        <v>1.765244746820827e-06</v>
       </c>
       <c r="FI6" t="n">
-        <v>9.206132745021023e-06</v>
+        <v>1.542599420645274e-06</v>
       </c>
       <c r="FJ6" t="n">
-        <v>8.968333531811368e-06</v>
+        <v>1.375583565277338e-06</v>
       </c>
       <c r="FK6" t="n">
-        <v>4.186370460956823e-06</v>
+        <v>1.332076067228627e-06</v>
       </c>
       <c r="FL6" t="n">
-        <v>1.970880475710146e-06</v>
+        <v>1.393627712786838e-06</v>
       </c>
       <c r="FM6" t="n">
-        <v>1.510243691882351e-06</v>
+        <v>6.332853104140668e-07</v>
       </c>
       <c r="FN6" t="n">
-        <v>6.76178433423047e-06</v>
+        <v>1.581032961439632e-06</v>
       </c>
       <c r="FO6" t="n">
-        <v>8.630776392237749e-06</v>
+        <v>2.066088882202166e-06</v>
       </c>
       <c r="FP6" t="n">
-        <v>9.205494279740378e-06</v>
+        <v>1.517505893389171e-06</v>
       </c>
       <c r="FQ6" t="n">
-        <v>1.334593434876297e-05</v>
+        <v>2.842613639586489e-06</v>
       </c>
       <c r="FR6" t="n">
-        <v>5.184245310374536e-06</v>
+        <v>9.303283263761841e-07</v>
       </c>
       <c r="FS6" t="n">
-        <v>4.058199465362122e-07</v>
+        <v>2.644017058628378e-06</v>
       </c>
       <c r="FT6" t="n">
-        <v>4.301669832784683e-06</v>
+        <v>2.63338023387405e-07</v>
       </c>
       <c r="FU6" t="n">
-        <v>1.671147856541211e-06</v>
+        <v>4.933930313200108e-07</v>
       </c>
       <c r="FV6" t="n">
-        <v>1.132641773438081e-05</v>
+        <v>4.523276402323972e-07</v>
       </c>
       <c r="FW6" t="n">
-        <v>6.096419838286238e-06</v>
+        <v>2.164860461562057e-06</v>
       </c>
       <c r="FX6" t="n">
-        <v>2.373586312387488e-06</v>
+        <v>7.514857429669064e-07</v>
       </c>
       <c r="FY6" t="n">
-        <v>1.316437555942684e-05</v>
+        <v>1.578700192794713e-08</v>
       </c>
       <c r="FZ6" t="n">
-        <v>4.232941591908457e-06</v>
+        <v>3.297811872471357e-07</v>
       </c>
       <c r="GA6" t="n">
-        <v>1.121484615396184e-06</v>
+        <v>1.805299916668446e-06</v>
       </c>
       <c r="GB6" t="n">
-        <v>2.892496468120953e-06</v>
+        <v>1.124534833252255e-06</v>
       </c>
       <c r="GC6" t="n">
-        <v>2.371674327150686e-06</v>
+        <v>2.982329760925495e-06</v>
       </c>
       <c r="GD6" t="n">
-        <v>8.969400369096547e-06</v>
+        <v>1.480754690419417e-06</v>
       </c>
       <c r="GE6" t="n">
-        <v>2.202150972152594e-05</v>
+        <v>7.528687433477899e-07</v>
       </c>
       <c r="GF6" t="n">
-        <v>4.231344973959494e-06</v>
+        <v>8.489519132126588e-08</v>
       </c>
       <c r="GG6" t="n">
-        <v>3.136955797344854e-07</v>
+        <v>3.383843534265907e-07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.001361838425509632</v>
+        <v>2.04657158064947e-06</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0106643196195364</v>
+        <v>1.084972063836176e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001254528295248747</v>
+        <v>3.618080882006325e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005656022578477859</v>
+        <v>3.329746050440008e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002176459413021803</v>
+        <v>3.400195510039339e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008275041356682777</v>
+        <v>2.055983168247622e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002144711907021701</v>
+        <v>2.003585905185901e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002766638994216919</v>
+        <v>3.685696583488607e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007744202157482505</v>
+        <v>7.362393716903171e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002623410196974874</v>
+        <v>1.087030568669434e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009661531075835228</v>
+        <v>1.122971661970951e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004673752700909972</v>
+        <v>5.703473107132595e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.004485262092202902</v>
+        <v>5.784429504274158e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>1.687026815488935e-05</v>
+        <v>4.224674285069341e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008179597556591034</v>
+        <v>2.421058525214903e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00082922208821401</v>
+        <v>1.427017991773027e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00133428000845015</v>
+        <v>5.498575319506926e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0005664055934175849</v>
+        <v>1.736178546707379e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002129242056980729</v>
+        <v>2.170126208511647e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0009442236041650176</v>
+        <v>1.759132146617048e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0007508416892960668</v>
+        <v>8.73461658557062e-07</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00209237146191299</v>
+        <v>3.860285232804017e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0007024758378975093</v>
+        <v>1.445586690351774e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0004338131984695792</v>
+        <v>3.120822384516941e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0006049360381439328</v>
+        <v>1.288583462155657e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001222181133925915</v>
+        <v>3.55788165506965e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0009626711253076792</v>
+        <v>1.447741738047625e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.03439805470407e-05</v>
+        <v>2.274670805491041e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0004183519340585917</v>
+        <v>1.201195004796318e-06</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0001990422897506505</v>
+        <v>3.129714968963526e-06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0003092772385571152</v>
+        <v>4.332999196776655e-06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0002541809226386249</v>
+        <v>3.823820861725835e-06</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.234093598322943e-05</v>
+        <v>3.339619297548779e-06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0002930510090664029</v>
+        <v>7.940864179545315e-07</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0003623785160016268</v>
+        <v>8.088580216281116e-06</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001041897805407643</v>
+        <v>1.824217633838998e-06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.001391750760376453</v>
+        <v>3.01336308439204e-06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.00124379200860858</v>
+        <v>2.915137201853213e-06</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0004374646523501724</v>
+        <v>2.142898665624671e-06</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0001980360539164394</v>
+        <v>2.312270225957036e-06</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0001999002124648541</v>
+        <v>2.560424036346376e-06</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.001369167119264603</v>
+        <v>2.030568339250749e-06</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0002670926041901112</v>
+        <v>6.389311693055788e-07</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.000888258102349937</v>
+        <v>4.090827587788226e-06</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.001781320665031672</v>
+        <v>1.862638441707531e-06</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0004694266535807401</v>
+        <v>1.409533069818281e-06</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.006438353098928928</v>
+        <v>1.050975060934434e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0004687793843913823</v>
+        <v>4.772193733515451e-06</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.001444283640012145</v>
+        <v>8.319411790580489e-07</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.002052802592515945</v>
+        <v>2.985998435178772e-06</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.00426673237234354</v>
+        <v>1.373470058751991e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.000647201610263437</v>
+        <v>1.5158088899625e-06</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0007895983289927244</v>
+        <v>2.030584028034355e-06</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.002655815333127975</v>
+        <v>4.091031087227748e-07</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.001166149158962071</v>
+        <v>4.197215730528114e-07</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.002171223051846027</v>
+        <v>1.490947397542186e-06</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.003357685869559646</v>
+        <v>2.280768285345403e-06</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0008783454541116953</v>
+        <v>2.396493982814718e-06</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.001509717549197376</v>
+        <v>3.204044787707971e-06</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.002313419710844755</v>
+        <v>1.109202230509254e-06</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0001900462084449828</v>
+        <v>3.559436208888656e-06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.001360035035759211</v>
+        <v>2.894097633543424e-06</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0006632305448874831</v>
+        <v>1.68463282079756e-06</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0002418644144199789</v>
+        <v>5.854226401424967e-07</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.002210212871432304</v>
+        <v>4.002730747743044e-06</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001242284546606243</v>
+        <v>7.604910479130922e-07</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001039435504935682</v>
+        <v>2.371629079789273e-06</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.911217107903212e-05</v>
+        <v>9.396923132953816e-07</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0006520016468130052</v>
+        <v>1.431225200576591e-06</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.000864656176418066</v>
+        <v>2.266476712975418e-06</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0009447832126170397</v>
+        <v>1.47211369494471e-06</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0002064050349872559</v>
+        <v>2.75597267318517e-06</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0001571586617501453</v>
+        <v>1.138968968916743e-06</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.003537500509992242</v>
+        <v>6.060202395019587e-06</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.001235536648891866</v>
+        <v>6.919797783666581e-07</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.001492345705628395</v>
+        <v>2.034305452980334e-07</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0008966822060756385</v>
+        <v>2.212855179095641e-07</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.001826900406740606</v>
+        <v>8.71670272317715e-06</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0005416743224486709</v>
+        <v>3.595977659642813e-06</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0006860897992737591</v>
+        <v>1.50568507706339e-06</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.001385903335176408</v>
+        <v>5.212852443037264e-07</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0001138567313319072</v>
+        <v>3.797172780650726e-07</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.001765231834724545</v>
+        <v>4.053581051266519e-06</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.00117918848991394</v>
+        <v>8.389058052671317e-07</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0008787063998170197</v>
+        <v>6.467844855251315e-07</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0004446656093932688</v>
+        <v>5.771743190052803e-07</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.001132333418354392</v>
+        <v>4.90994125357247e-06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0005318910116329789</v>
+        <v>6.991700161051995e-07</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0006269293371587992</v>
+        <v>8.523805377080862e-07</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0009518828592263162</v>
+        <v>1.962407338851335e-07</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.002188831800594926</v>
+        <v>2.025732555921422e-06</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0004644031869247556</v>
+        <v>3.688984179461841e-06</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0002385110419709235</v>
+        <v>4.332599019107874e-06</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.001448785304091871</v>
+        <v>2.249453245894983e-06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0004126890562474728</v>
+        <v>1.155342715719598e-06</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.001509485999122262</v>
+        <v>4.499073043007229e-07</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.001974331447854638</v>
+        <v>4.050850293424446e-06</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.001453984994441271</v>
+        <v>4.379517122288235e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0003108708187937737</v>
+        <v>1.634134605410509e-09</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0001487386325607076</v>
+        <v>6.729373467351252e-07</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.001639951369725168</v>
+        <v>3.826848569588037e-06</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0011876035714522</v>
+        <v>1.422867057954136e-06</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.001385576790198684</v>
+        <v>1.430916199751664e-06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0002083133440464735</v>
+        <v>6.702100563416025e-08</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.001224398263730109</v>
+        <v>5.561219040828291e-06</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0005143784219399095</v>
+        <v>1.68367279229642e-07</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.001342467265203595</v>
+        <v>1.109230765905522e-06</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0006189816631376743</v>
+        <v>1.229240922384633e-07</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0009618762414902449</v>
+        <v>8.839902534418798e-07</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0004661837592720985</v>
+        <v>7.066280431899941e-06</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0002865552087314427</v>
+        <v>4.285897375666536e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.002798949833959341</v>
+        <v>2.702526217035484e-06</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.002453880617395043</v>
+        <v>2.793724434013711e-07</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.001276489114388824</v>
+        <v>3.590000460462761e-06</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0009920911397784948</v>
+        <v>5.63853859603114e-07</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.001890562009066343</v>
+        <v>5.34758373760269e-06</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.002306570298969746</v>
+        <v>4.337871814641403e-06</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0003995037404820323</v>
+        <v>1.304025317949709e-06</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.000646676286123693</v>
+        <v>4.933482159685809e-06</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0005317771574482322</v>
+        <v>7.345799986069323e-07</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0002888093295041472</v>
+        <v>1.013280325423693e-06</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0003928731894120574</v>
+        <v>1.905139583868731e-06</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0006743873236700892</v>
+        <v>3.798275201916113e-06</v>
       </c>
       <c r="DT7" t="n">
-        <v>6.227396079339087e-05</v>
+        <v>1.491529474151321e-06</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0002624704211484641</v>
+        <v>4.545418050838634e-06</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.001238542376086116</v>
+        <v>2.074905012250383e-07</v>
       </c>
       <c r="DW7" t="n">
-        <v>2.069544279947877e-05</v>
+        <v>7.827727586118272e-07</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0008579897112213075</v>
+        <v>3.033303386246189e-08</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.001335086300969124</v>
+        <v>5.571041583607439e-06</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0003045467892661691</v>
+        <v>5.887441290042261e-08</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0007349404040724039</v>
+        <v>1.583135599503294e-06</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0007109990692697465</v>
+        <v>1.916035216709133e-06</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0004269634955562651</v>
+        <v>1.94475319403864e-06</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0004889930132776499</v>
+        <v>2.081128286590683e-06</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0007405992946587503</v>
+        <v>5.354286713554757e-06</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.001067471690475941</v>
+        <v>3.291309269570775e-07</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.001798357116058469</v>
+        <v>4.332973446707911e-07</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.001414262223988771</v>
+        <v>4.10307734455273e-07</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0006022201851010323</v>
+        <v>1.67075768331415e-06</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0004329279181547463</v>
+        <v>2.197448793594958e-06</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.00123670557513833</v>
+        <v>2.033129021583591e-06</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.0005706184892915189</v>
+        <v>1.649512171297829e-07</v>
       </c>
       <c r="EM7" t="n">
-        <v>1.353859443042893e-05</v>
+        <v>1.972120600157723e-07</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0002690974506549537</v>
+        <v>8.787749266048195e-07</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0001294189714826643</v>
+        <v>5.011580128666537e-08</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0009925991762429476</v>
+        <v>2.322711907254416e-06</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.001089011551812291</v>
+        <v>1.177412173092307e-06</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0008322207722812891</v>
+        <v>3.312258058940643e-06</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0006888809148222208</v>
+        <v>3.873929927067365e-06</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0007815101416781545</v>
+        <v>1.641895721604669e-07</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.001555167837068439</v>
+        <v>1.91854724107543e-07</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.003056087298318744</v>
+        <v>3.53646044004563e-07</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0001696671242825687</v>
+        <v>1.620605871721637e-06</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0003870196524076164</v>
+        <v>1.901341306620452e-07</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.001549448585137725</v>
+        <v>4.14330361309112e-06</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0009962074691429734</v>
+        <v>8.152993018484267e-07</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.001074153347872198</v>
+        <v>1.386079247822636e-06</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0002961384598165751</v>
+        <v>8.369713668798795e-07</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.0009365743026137352</v>
+        <v>5.344882083591074e-06</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0008816376212053001</v>
+        <v>1.294739149670932e-06</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0009156716405414045</v>
+        <v>1.19213245852734e-06</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.001011420274153352</v>
+        <v>1.016045189317083e-06</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0006247606943361461</v>
+        <v>3.538805515290733e-08</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.0003667950222734362</v>
+        <v>2.500723894627299e-06</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.001161877531558275</v>
+        <v>3.47796003552503e-06</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.001567943603731692</v>
+        <v>2.296031425430556e-06</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0001209484180435538</v>
+        <v>6.260859208850889e-08</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.001766754314303398</v>
+        <v>6.937804755580146e-06</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0001539748918730766</v>
+        <v>1.027447751766886e-06</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.001375369029119611</v>
+        <v>6.018906333338236e-06</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0005193491233512759</v>
+        <v>4.814255134988343e-06</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.001222069375216961</v>
+        <v>3.770516968870652e-06</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.0006008771015331149</v>
+        <v>3.33115804096451e-06</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.001362321199849248</v>
+        <v>3.059076561839902e-06</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.00104407430626452</v>
+        <v>3.877772087435005e-06</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001855496666394174</v>
+        <v>1.103172166949662e-06</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0006675805198028684</v>
+        <v>4.393602466734592e-06</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0008926786249503493</v>
+        <v>3.357068180775968e-06</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0008118455880321562</v>
+        <v>9.797948223422281e-06</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0001656275126151741</v>
+        <v>8.836625511321472e-07</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.002082752995193005</v>
+        <v>2.008793671848252e-06</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0006758284289389849</v>
+        <v>8.134800850712054e-07</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0009074007393792272</v>
+        <v>4.265197276254185e-06</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0004637769889086485</v>
+        <v>3.904392542608548e-08</v>
       </c>
       <c r="GC7" t="n">
-        <v>2.045344444923103e-05</v>
+        <v>7.471867775166174e-06</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.0009518374572508037</v>
+        <v>3.466039061095216e-06</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.004179020412266254</v>
+        <v>1.556839492877771e-06</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0003179261984769255</v>
+        <v>2.284733227497782e-06</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.00107607536483556</v>
+        <v>8.546584240320954e-07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0001147457587649114</v>
+        <v>5.254971124912799e-09</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001992737874388695</v>
+        <v>2.948681476766524e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.227219662629068e-05</v>
+        <v>1.10607354386616e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000799559464212507</v>
+        <v>1.159300389019791e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0008278641616925597</v>
+        <v>7.986715289121094e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001053950050845742</v>
+        <v>3.090994127319391e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.505165508016944e-05</v>
+        <v>8.857348632318462e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0002813252503983676</v>
+        <v>6.790759954355963e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004611325566656888</v>
+        <v>1.430993279427639e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001412927522324026</v>
+        <v>2.338942373114605e-10</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002197798807173967</v>
+        <v>3.634021439324897e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001405476359650493</v>
+        <v>2.005875288091374e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002688507956918329</v>
+        <v>3.048709729114307e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0002966428874060512</v>
+        <v>1.594445464547789e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0008116738754324615</v>
+        <v>4.229938710409442e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.630411811172962e-06</v>
+        <v>1.75469305752074e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.721029548207298e-05</v>
+        <v>2.422261502488254e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0003582530771382153</v>
+        <v>1.268235294560327e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>1.621720002731308e-06</v>
+        <v>8.904931236841662e-10</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0002622453612275422</v>
+        <v>9.198300787716107e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0001638927788008004</v>
+        <v>2.618774530560586e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002119803975801915</v>
+        <v>5.216461040902232e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001552283647470176</v>
+        <v>9.524830701934661e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>3.97556577809155e-05</v>
+        <v>9.558808855558709e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.623149965889752e-05</v>
+        <v>1.065517629683654e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0001136506616603583</v>
+        <v>7.315478889324822e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0002174243418266997</v>
+        <v>7.111945699023181e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.084821896161884e-05</v>
+        <v>1.225815804417607e-08</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0001557536888867617</v>
+        <v>2.366492557470679e-09</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0003725546994246542</v>
+        <v>1.215694656053756e-09</v>
       </c>
       <c r="AE8" t="n">
-        <v>8.178774442058057e-05</v>
+        <v>1.381763858887552e-08</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0001221561687998474</v>
+        <v>1.306287700231223e-08</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.000190870588994585</v>
+        <v>1.785784853325367e-08</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0001817459560697898</v>
+        <v>4.134697917379526e-09</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.561165405903012e-05</v>
+        <v>3.233087042531224e-08</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0001094649342121556</v>
+        <v>3.77334252732453e-09</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0003086382930632681</v>
+        <v>9.761523811491202e-10</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0003423391317483038</v>
+        <v>8.297135423163127e-09</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0002544525486882776</v>
+        <v>7.996829864964639e-10</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.071394308382878e-05</v>
+        <v>1.643403413353894e-09</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.288147814193508e-05</v>
+        <v>4.524686403328815e-09</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0001647414319450036</v>
+        <v>4.199928405057562e-09</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.896607374073938e-05</v>
+        <v>8.515011806764505e-09</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.815042898873799e-05</v>
+        <v>9.372582709943345e-09</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.049125345773064e-05</v>
+        <v>2.531913567693778e-09</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.000144457706483081</v>
+        <v>6.444261124727291e-09</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001316203502938151</v>
+        <v>4.30956035302188e-08</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0004082614905200899</v>
+        <v>6.01814509337828e-09</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0002512235078029335</v>
+        <v>3.241227286565618e-09</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.729025775101036e-05</v>
+        <v>2.422826916870235e-08</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0004840182955376804</v>
+        <v>3.145759208678101e-08</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0001629677717573941</v>
+        <v>9.082528507065035e-09</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.894184555974789e-05</v>
+        <v>1.209487621167682e-09</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0001028583064908162</v>
+        <v>3.101913614855789e-09</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.426069062901661e-05</v>
+        <v>7.688473857569988e-09</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0004068098496645689</v>
+        <v>9.362567610082806e-09</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0002741773787420243</v>
+        <v>1.267456006814882e-08</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.501012542983517e-05</v>
+        <v>1.584727193915114e-08</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0006433426751755178</v>
+        <v>8.446086496860516e-09</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0004126587009523064</v>
+        <v>1.188578124811102e-10</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0001403780916007236</v>
+        <v>3.092234024393292e-09</v>
       </c>
       <c r="BJ8" t="n">
-        <v>6.128394306870177e-05</v>
+        <v>1.315665887346995e-08</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.972046634880826e-05</v>
+        <v>1.840593277790958e-08</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.000290845287963748</v>
+        <v>9.74474945181214e-11</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0002831568708643317</v>
+        <v>1.117686299068055e-08</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.898415111005306e-05</v>
+        <v>1.743151401001342e-09</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0001106990966945887</v>
+        <v>2.930201192796744e-09</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002392923051957041</v>
+        <v>7.261733436791928e-09</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.244488157681189e-05</v>
+        <v>2.847515778725551e-09</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0001155133213615045</v>
+        <v>1.141322236719589e-08</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.41185319586657e-05</v>
+        <v>5.088790278051647e-09</v>
       </c>
       <c r="BT8" t="n">
-        <v>3.51184826286044e-05</v>
+        <v>1.263210869240083e-08</v>
       </c>
       <c r="BU8" t="n">
-        <v>9.448756463825703e-05</v>
+        <v>2.510006646971874e-09</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0008316424791701138</v>
+        <v>2.358460982065935e-08</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0001812140981201082</v>
+        <v>5.837708094702521e-11</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0001947477285284549</v>
+        <v>1.504745217317804e-09</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.107988909003325e-05</v>
+        <v>6.330366453255465e-09</v>
       </c>
       <c r="BZ8" t="n">
-        <v>7.960444781929255e-05</v>
+        <v>2.267048770931979e-08</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.13043515739264e-05</v>
+        <v>6.287367515511733e-09</v>
       </c>
       <c r="CB8" t="n">
-        <v>2.004394445975777e-05</v>
+        <v>2.721298741903411e-09</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.057473804801702e-05</v>
+        <v>2.21829221658254e-09</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.388549107010476e-05</v>
+        <v>2.728893111481057e-09</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0003378799301572144</v>
+        <v>1.036500751894209e-08</v>
       </c>
       <c r="CF8" t="n">
-        <v>1.003506622510031e-05</v>
+        <v>2.010781763317482e-09</v>
       </c>
       <c r="CG8" t="n">
-        <v>8.230000821640715e-05</v>
+        <v>2.68484035004235e-09</v>
       </c>
       <c r="CH8" t="n">
-        <v>2.804171708703507e-05</v>
+        <v>2.7335342878132e-09</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0002133354864781722</v>
+        <v>7.894500164695728e-09</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0001393337297486141</v>
+        <v>2.579575719696692e-10</v>
       </c>
       <c r="CK8" t="n">
-        <v>2.358392339374404e-05</v>
+        <v>3.804104586890844e-09</v>
       </c>
       <c r="CL8" t="n">
-        <v>7.257518882397562e-05</v>
+        <v>4.574208567476035e-09</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0005488384631462395</v>
+        <v>3.726551955907098e-09</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0002069904730888084</v>
+        <v>1.274741823209524e-08</v>
       </c>
       <c r="CO8" t="n">
-        <v>6.224830576684326e-05</v>
+        <v>1.136419403025002e-08</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0003048241487704217</v>
+        <v>1.854544606771924e-08</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0003079967282246798</v>
+        <v>3.561311912037013e-09</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0001870063570095226</v>
+        <v>1.420573703114769e-08</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0004578241205308586</v>
+        <v>4.665166919437524e-09</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0002721179334912449</v>
+        <v>1.525020820736245e-08</v>
       </c>
       <c r="CU8" t="n">
-        <v>5.213748954702169e-05</v>
+        <v>1.422999162947747e-09</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.345443979516858e-05</v>
+        <v>3.271984905239833e-09</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0003220791695639491</v>
+        <v>9.707968651184729e-09</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.986026836675592e-05</v>
+        <v>2.934281262412242e-09</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0001540858211228624</v>
+        <v>6.075046243836368e-09</v>
       </c>
       <c r="CZ8" t="n">
-        <v>6.704118277411908e-05</v>
+        <v>4.047051138655888e-09</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.000227957745664753</v>
+        <v>1.022266893357937e-08</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0001509905705461279</v>
+        <v>1.170559649210645e-09</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.000104973471025005</v>
+        <v>4.240918727305143e-09</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.539780638879165e-05</v>
+        <v>3.965982209308549e-09</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0002274831931572407</v>
+        <v>4.662025876456255e-09</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0003121421614196151</v>
+        <v>4.37835545596954e-09</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.870359483291395e-05</v>
+        <v>7.892300146750131e-10</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.000501906790304929</v>
+        <v>3.720672214768683e-09</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0005226817447692156</v>
+        <v>1.055793674709093e-09</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0002332027652300894</v>
+        <v>8.605115731086244e-09</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.387662142515182e-05</v>
+        <v>2.089186823539535e-09</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0001645368174649775</v>
+        <v>1.581596364985671e-08</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0002311649004695937</v>
+        <v>3.061249476132843e-09</v>
       </c>
       <c r="DN8" t="n">
-        <v>9.034486720338464e-05</v>
+        <v>4.642330964088615e-09</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.68266415130347e-05</v>
+        <v>8.777821802752328e-10</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0001187070956802927</v>
+        <v>2.678524513299863e-09</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0001539940712973475</v>
+        <v>5.835619543148596e-09</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001560067030368373</v>
+        <v>6.978809086177762e-09</v>
       </c>
       <c r="DS8" t="n">
-        <v>9.633526497054845e-05</v>
+        <v>2.921008768197453e-09</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0001102802343666553</v>
+        <v>6.495318061183752e-09</v>
       </c>
       <c r="DU8" t="n">
-        <v>7.937577902339399e-05</v>
+        <v>1.368071078644562e-08</v>
       </c>
       <c r="DV8" t="n">
-        <v>4.677134711528197e-05</v>
+        <v>5.18601783738859e-09</v>
       </c>
       <c r="DW8" t="n">
-        <v>7.776875281706452e-05</v>
+        <v>1.932061843845645e-09</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.000162773285410367</v>
+        <v>6.817629571997941e-09</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.910483378102072e-05</v>
+        <v>9.232692832483735e-09</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.557166489074007e-05</v>
+        <v>9.007696810670041e-09</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0001089892029995099</v>
+        <v>5.524311230686862e-09</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0001881782955024391</v>
+        <v>3.079603239086737e-10</v>
       </c>
       <c r="EC8" t="n">
-        <v>7.452978752553463e-05</v>
+        <v>3.190169461930736e-09</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0001863539946498349</v>
+        <v>1.19798411191141e-08</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0002595514233689755</v>
+        <v>7.846233884833964e-09</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0001999970991164446</v>
+        <v>1.564239626716812e-09</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0004296858969610184</v>
+        <v>2.850331082271396e-09</v>
       </c>
       <c r="EH8" t="n">
-        <v>6.37420525890775e-05</v>
+        <v>4.211154980282572e-09</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0001169673632830381</v>
+        <v>2.074675986563079e-09</v>
       </c>
       <c r="EJ8" t="n">
-        <v>8.996279939310625e-05</v>
+        <v>1.902062285452644e-09</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0001756296842359006</v>
+        <v>8.472029744410747e-10</v>
       </c>
       <c r="EL8" t="n">
-        <v>4.874947626376525e-05</v>
+        <v>8.105748017239733e-11</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0001624841243028641</v>
+        <v>3.576677842787035e-11</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.000121223485621158</v>
+        <v>1.577598718327522e-09</v>
       </c>
       <c r="EO8" t="n">
-        <v>1.965510455192998e-05</v>
+        <v>3.240458346098762e-09</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0002878775703720748</v>
+        <v>5.768656219373725e-09</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0001273889793083072</v>
+        <v>1.117106962489345e-09</v>
       </c>
       <c r="ER8" t="n">
-        <v>2.259246684843674e-05</v>
+        <v>2.002890298058446e-09</v>
       </c>
       <c r="ES8" t="n">
-        <v>4.31921289418824e-05</v>
+        <v>4.234497197330711e-10</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0001362348411930725</v>
+        <v>1.131174975910199e-08</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0002107229520333931</v>
+        <v>5.802959890388593e-09</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0003634685999713838</v>
+        <v>4.784533658153123e-09</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0001237956894328818</v>
+        <v>1.271071359276732e-09</v>
       </c>
       <c r="EX8" t="n">
-        <v>6.902849418111145e-05</v>
+        <v>2.889724903809565e-09</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0003136974992230535</v>
+        <v>1.177180752875984e-08</v>
       </c>
       <c r="EZ8" t="n">
-        <v>6.537462468259037e-05</v>
+        <v>9.3012247903701e-10</v>
       </c>
       <c r="FA8" t="n">
-        <v>7.14795824023895e-05</v>
+        <v>6.389665685446744e-09</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0001031148203765042</v>
+        <v>1.53741130937135e-09</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0002217996516264975</v>
+        <v>7.159668857781298e-09</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0001313655229751021</v>
+        <v>1.025813808896991e-10</v>
       </c>
       <c r="FE8" t="n">
-        <v>4.17632945755031e-05</v>
+        <v>1.117774761638657e-09</v>
       </c>
       <c r="FF8" t="n">
-        <v>8.236434223363176e-05</v>
+        <v>9.400100697831704e-10</v>
       </c>
       <c r="FG8" t="n">
-        <v>2.304347799508832e-05</v>
+        <v>2.167943824460394e-09</v>
       </c>
       <c r="FH8" t="n">
-        <v>9.96455637505278e-05</v>
+        <v>9.834749015169564e-09</v>
       </c>
       <c r="FI8" t="n">
-        <v>2.876204962376505e-05</v>
+        <v>6.430386889633155e-09</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.0003611567663028836</v>
+        <v>6.542599795267279e-09</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0001213771902257577</v>
+        <v>4.310201084933851e-09</v>
       </c>
       <c r="FL8" t="n">
-        <v>3.605147139751352e-05</v>
+        <v>1.735846133499308e-08</v>
       </c>
       <c r="FM8" t="n">
-        <v>6.892462988616899e-05</v>
+        <v>2.240072127790427e-09</v>
       </c>
       <c r="FN8" t="n">
-        <v>9.501137537881732e-05</v>
+        <v>5.626816790282874e-09</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0001195080840261653</v>
+        <v>1.946755112669507e-08</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0002825947012752295</v>
+        <v>2.567550616561221e-10</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0001982742105610669</v>
+        <v>1.736759713821812e-08</v>
       </c>
       <c r="FR8" t="n">
-        <v>6.77724092383869e-05</v>
+        <v>1.573149077671587e-08</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0001205373700940982</v>
+        <v>2.497740014817396e-09</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0004858171159867197</v>
+        <v>2.64564938845524e-08</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0001103042814065702</v>
+        <v>3.36000627321198e-09</v>
       </c>
       <c r="FV8" t="n">
-        <v>4.539125075098127e-05</v>
+        <v>4.173553946884567e-09</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0003813994990196079</v>
+        <v>1.098109070341025e-08</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0001315969857387245</v>
+        <v>1.039083930010065e-09</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.0002402102691121399</v>
+        <v>1.524604664737694e-09</v>
       </c>
       <c r="FZ8" t="n">
-        <v>6.700780795654282e-05</v>
+        <v>9.8770402967574e-10</v>
       </c>
       <c r="GA8" t="n">
-        <v>4.184751742286608e-05</v>
+        <v>9.567225234263788e-09</v>
       </c>
       <c r="GB8" t="n">
-        <v>3.865869803121313e-05</v>
+        <v>5.071784769938859e-09</v>
       </c>
       <c r="GC8" t="n">
-        <v>9.763924026628956e-05</v>
+        <v>1.948775540938641e-08</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0001713573437882587</v>
+        <v>1.665457993738073e-08</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.0001805985230021179</v>
+        <v>3.950614058112478e-09</v>
       </c>
       <c r="GF8" t="n">
-        <v>4.830855687032454e-05</v>
+        <v>1.223109169501413e-09</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0002937118115369231</v>
+        <v>1.918811332046744e-09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.716192049583398e-10</v>
+        <v>6.268781937990298e-09</v>
       </c>
       <c r="B9" t="n">
-        <v>3.974667539541343e-10</v>
+        <v>2.247173114255929e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.938770845255622e-11</v>
+        <v>8.622447200679062e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>5.330957897342614e-10</v>
+        <v>7.251645062211765e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>2.848556113210776e-10</v>
+        <v>2.990438119354621e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>2.924155362293845e-11</v>
+        <v>1.926008152963732e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.168814849934364e-10</v>
+        <v>3.581481777814588e-10</v>
       </c>
       <c r="H9" t="n">
-        <v>5.450299586651219e-11</v>
+        <v>6.972189048326527e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>1.396419230248469e-10</v>
+        <v>3.929645053801778e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>2.062740811492603e-10</v>
+        <v>8.227574177510633e-10</v>
       </c>
       <c r="K9" t="n">
-        <v>2.781476160507168e-10</v>
+        <v>2.656967623693163e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.852943741306959e-11</v>
+        <v>4.61693083764203e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>2.032911755600608e-10</v>
+        <v>1.465307253312176e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.933068870587419e-10</v>
+        <v>1.184990061631197e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>2.789038999750915e-10</v>
+        <v>2.099960916268628e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.493792949920248e-10</v>
+        <v>1.901562018957748e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.647277730887353e-10</v>
+        <v>1.443082098262494e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>1.563808804672107e-10</v>
+        <v>4.104207640409641e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>2.858999495480852e-11</v>
+        <v>3.373783474813763e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.484122685857514e-10</v>
+        <v>8.712675025890348e-11</v>
       </c>
       <c r="U9" t="n">
-        <v>5.914090051017951e-11</v>
+        <v>2.858123515636635e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>3.384079908658189e-12</v>
+        <v>4.397660902100142e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>3.104515811092057e-10</v>
+        <v>2.201760551656662e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.495893686698224e-10</v>
+        <v>2.310920566017671e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.9336231227296e-10</v>
+        <v>2.939568144455507e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.332844499854716e-11</v>
+        <v>2.321386638470813e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.276923566884136e-10</v>
+        <v>3.87794851786083e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.843884073204904e-11</v>
+        <v>8.775060678090085e-10</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.790022574610362e-10</v>
+        <v>6.568757093816657e-09</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.270188398905248e-10</v>
+        <v>8.435152576424798e-10</v>
       </c>
       <c r="AE9" t="n">
-        <v>5.859573937172513e-11</v>
+        <v>3.365926648513096e-09</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.900682389255337e-10</v>
+        <v>7.611760111103649e-09</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.847133888181588e-11</v>
+        <v>9.672234568824933e-09</v>
       </c>
       <c r="AH9" t="n">
-        <v>9.64499521916018e-11</v>
+        <v>1.274270355899887e-09</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.310327706396166e-11</v>
+        <v>1.368639335197486e-08</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7.064147183877267e-11</v>
+        <v>1.020322715206134e-09</v>
       </c>
       <c r="AK9" t="n">
-        <v>8.821840480344179e-11</v>
+        <v>4.819664223276732e-09</v>
       </c>
       <c r="AL9" t="n">
-        <v>8.249412264405009e-11</v>
+        <v>3.866821529641129e-09</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.489693339326806e-11</v>
+        <v>6.786379014300792e-09</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.028023665141433e-11</v>
+        <v>2.700789814014115e-09</v>
       </c>
       <c r="AO9" t="n">
-        <v>4.538798156761281e-12</v>
+        <v>2.293456535795713e-09</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.539532969642494e-11</v>
+        <v>2.74540923328459e-09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.532949098885354e-11</v>
+        <v>2.426951528633481e-09</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.390357412534016e-10</v>
+        <v>1.725176113076543e-09</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.649997219554393e-11</v>
+        <v>3.22427951005011e-09</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.606173858474506e-11</v>
+        <v>6.041169342552166e-09</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.010611538372231e-10</v>
+        <v>1.943920402425192e-08</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.740311193765276e-11</v>
+        <v>7.881230779105408e-09</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.989404834785603e-10</v>
+        <v>2.01072936079072e-09</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.362151641481901e-10</v>
+        <v>2.075187310879301e-08</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.305857089128892e-10</v>
+        <v>1.811489092062857e-08</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.283583127622336e-11</v>
+        <v>3.0854581112294e-09</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.996706438025299e-11</v>
+        <v>3.185577135411677e-09</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.161077369450709e-11</v>
+        <v>2.129343590340227e-09</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.515373657256518e-11</v>
+        <v>1.994663545445974e-09</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.418888420263059e-11</v>
+        <v>3.413486160397383e-09</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.210099267103033e-11</v>
+        <v>2.112809482923694e-09</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.759414571840146e-11</v>
+        <v>7.513299316030952e-09</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.524208619902879e-10</v>
+        <v>6.551040598878899e-09</v>
       </c>
       <c r="BH9" t="n">
-        <v>1.359040241455389e-10</v>
+        <v>2.414890731827768e-09</v>
       </c>
       <c r="BI9" t="n">
-        <v>9.412933106578425e-12</v>
+        <v>5.153936832869022e-09</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.941064114996394e-10</v>
+        <v>1.033189445109883e-08</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.765943972280141e-11</v>
+        <v>7.532149348676853e-10</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.042592678857091e-10</v>
+        <v>1.445539243860594e-10</v>
       </c>
       <c r="BM9" t="n">
-        <v>4.04975358803128e-11</v>
+        <v>6.452186340766275e-09</v>
       </c>
       <c r="BN9" t="n">
-        <v>8.581566707244193e-11</v>
+        <v>1.736119026318761e-09</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.20121940172524e-10</v>
+        <v>1.227054458041721e-09</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.542180603335112e-11</v>
+        <v>7.604938900840352e-09</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.515596932151087e-11</v>
+        <v>6.916918149357798e-10</v>
       </c>
       <c r="BR9" t="n">
-        <v>9.624898100746293e-12</v>
+        <v>5.9149827258409e-09</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.639420626504574e-11</v>
+        <v>4.212158621896833e-09</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.093319681628074e-11</v>
+        <v>3.096895406784483e-09</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.136950512376945e-11</v>
+        <v>3.390156155802515e-09</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.434204558036782e-11</v>
+        <v>6.060538293439777e-09</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.239183723641631e-11</v>
+        <v>3.967266959392646e-09</v>
       </c>
       <c r="BX9" t="n">
-        <v>6.738580526910454e-11</v>
+        <v>1.619273604092086e-10</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.255170174549683e-11</v>
+        <v>2.859395831222855e-09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>6.610713365606813e-11</v>
+        <v>8.983935373407803e-09</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.223176560039008e-10</v>
+        <v>5.264603419874447e-09</v>
       </c>
       <c r="CB9" t="n">
-        <v>1.214897973889073e-12</v>
+        <v>2.330947435069675e-09</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.776451373838086e-11</v>
+        <v>3.498328293716213e-10</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.502589802055866e-11</v>
+        <v>2.359346606972679e-10</v>
       </c>
       <c r="CE9" t="n">
-        <v>7.800989715311957e-11</v>
+        <v>7.216682806898689e-09</v>
       </c>
       <c r="CF9" t="n">
-        <v>7.231793636153228e-11</v>
+        <v>2.112464647652246e-10</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.514326941094325e-11</v>
+        <v>2.058283987693699e-09</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.430861245460546e-11</v>
+        <v>2.455199821227438e-09</v>
       </c>
       <c r="CI9" t="n">
-        <v>3.857057034872824e-11</v>
+        <v>4.856852697798786e-09</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.597248722173816e-11</v>
+        <v>1.60694124673455e-10</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.401626124192257e-11</v>
+        <v>2.501244544816927e-09</v>
       </c>
       <c r="CL9" t="n">
-        <v>9.284163021705538e-11</v>
+        <v>2.088857753435036e-09</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.029715479550219e-10</v>
+        <v>4.522370034010237e-09</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.847286989515752e-11</v>
+        <v>7.874750629355276e-09</v>
       </c>
       <c r="CO9" t="n">
-        <v>4.03631884859923e-11</v>
+        <v>1.254867143529736e-08</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.265528792870896e-10</v>
+        <v>8.076048274574532e-09</v>
       </c>
       <c r="CQ9" t="n">
-        <v>1.160250645559913e-10</v>
+        <v>4.299615774527865e-09</v>
       </c>
       <c r="CR9" t="n">
-        <v>7.000564017367594e-11</v>
+        <v>2.670258902881528e-09</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.832725915473787e-10</v>
+        <v>1.160160967295099e-09</v>
       </c>
       <c r="CT9" t="n">
-        <v>5.800861874183383e-11</v>
+        <v>6.65402133392945e-09</v>
       </c>
       <c r="CU9" t="n">
-        <v>2.740604097828392e-11</v>
+        <v>4.955504895320928e-09</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.863376987432108e-11</v>
+        <v>1.452197362361574e-09</v>
       </c>
       <c r="CW9" t="n">
-        <v>7.294909121213777e-11</v>
+        <v>6.720001444193713e-09</v>
       </c>
       <c r="CX9" t="n">
-        <v>6.673743502272345e-11</v>
+        <v>6.344190728313492e-10</v>
       </c>
       <c r="CY9" t="n">
-        <v>7.128072437856403e-11</v>
+        <v>3.277670579393543e-09</v>
       </c>
       <c r="CZ9" t="n">
-        <v>3.621843797096957e-11</v>
+        <v>2.727856385220662e-09</v>
       </c>
       <c r="DA9" t="n">
-        <v>5.334130359635481e-11</v>
+        <v>5.831317206883568e-09</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.980383912414396e-11</v>
+        <v>9.761154107224002e-10</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.555314557699639e-11</v>
+        <v>1.959943318752266e-09</v>
       </c>
       <c r="DD9" t="n">
-        <v>8.188107136763989e-11</v>
+        <v>1.282444705985597e-09</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.135658650452953e-10</v>
+        <v>2.676230903553289e-10</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.466797378002482e-10</v>
+        <v>1.381493586194438e-09</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.384836967321945e-10</v>
+        <v>1.785675385335139e-09</v>
       </c>
       <c r="DH9" t="n">
-        <v>2.940500898329645e-10</v>
+        <v>2.408517829621815e-09</v>
       </c>
       <c r="DI9" t="n">
-        <v>4.882771964531685e-10</v>
+        <v>1.837290097839173e-09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.039115321566086e-10</v>
+        <v>9.004509138321737e-09</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.011601440976563e-10</v>
+        <v>2.262788845186492e-09</v>
       </c>
       <c r="DL9" t="n">
-        <v>3.178413088278376e-10</v>
+        <v>5.745679487745292e-09</v>
       </c>
       <c r="DM9" t="n">
-        <v>4.49838430394145e-11</v>
+        <v>2.946589194863236e-09</v>
       </c>
       <c r="DN9" t="n">
-        <v>6.493442589183829e-11</v>
+        <v>2.142732435927996e-09</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.62236282636097e-11</v>
+        <v>2.344060501258127e-09</v>
       </c>
       <c r="DP9" t="n">
-        <v>6.213531078547163e-11</v>
+        <v>1.609239963507036e-09</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.494165347004639e-10</v>
+        <v>4.47778480960892e-10</v>
       </c>
       <c r="DR9" t="n">
-        <v>3.186530900256557e-12</v>
+        <v>1.304033325766341e-09</v>
       </c>
       <c r="DS9" t="n">
-        <v>2.242020978593384e-11</v>
+        <v>3.886658772600526e-10</v>
       </c>
       <c r="DT9" t="n">
-        <v>1.131652063723898e-12</v>
+        <v>2.413466981820989e-09</v>
       </c>
       <c r="DU9" t="n">
-        <v>4.593940505781546e-11</v>
+        <v>6.187852896744062e-09</v>
       </c>
       <c r="DV9" t="n">
-        <v>1.623357698266048e-10</v>
+        <v>4.840981837617164e-09</v>
       </c>
       <c r="DW9" t="n">
-        <v>1.81563999945844e-11</v>
+        <v>2.743840932240005e-09</v>
       </c>
       <c r="DX9" t="n">
-        <v>2.267248541687472e-11</v>
+        <v>3.347888188898196e-09</v>
       </c>
       <c r="DY9" t="n">
-        <v>2.056855796794821e-10</v>
+        <v>5.63180257984186e-09</v>
       </c>
       <c r="DZ9" t="n">
-        <v>6.16876124834298e-12</v>
+        <v>3.063913345258129e-09</v>
       </c>
       <c r="EA9" t="n">
-        <v>2.394439507780177e-11</v>
+        <v>7.313501471095663e-10</v>
       </c>
       <c r="EB9" t="n">
-        <v>2.169740082047511e-10</v>
+        <v>3.915870294690649e-09</v>
       </c>
       <c r="EC9" t="n">
-        <v>9.045635768201166e-12</v>
+        <v>1.85792714546551e-10</v>
       </c>
       <c r="ED9" t="n">
-        <v>4.577598022859064e-11</v>
+        <v>9.520403132512456e-09</v>
       </c>
       <c r="EE9" t="n">
-        <v>1.445196740057497e-11</v>
+        <v>4.576754530916105e-09</v>
       </c>
       <c r="EF9" t="n">
-        <v>3.182811653124062e-12</v>
+        <v>2.566859613750694e-09</v>
       </c>
       <c r="EG9" t="n">
-        <v>7.656300593517074e-11</v>
+        <v>1.579193553702396e-09</v>
       </c>
       <c r="EH9" t="n">
-        <v>8.300565096375223e-11</v>
+        <v>2.530342158024723e-09</v>
       </c>
       <c r="EI9" t="n">
-        <v>7.876670149453702e-11</v>
+        <v>6.883825176551284e-10</v>
       </c>
       <c r="EJ9" t="n">
-        <v>7.301922955171847e-11</v>
+        <v>1.664984816684978e-09</v>
       </c>
       <c r="EK9" t="n">
-        <v>7.598963819299698e-11</v>
+        <v>3.467715448124409e-09</v>
       </c>
       <c r="EL9" t="n">
-        <v>3.676004639574515e-11</v>
+        <v>2.14759454664204e-09</v>
       </c>
       <c r="EM9" t="n">
-        <v>2.105410637498473e-11</v>
+        <v>4.539189857322157e-10</v>
       </c>
       <c r="EN9" t="n">
-        <v>7.617666913928289e-11</v>
+        <v>1.385310199886192e-10</v>
       </c>
       <c r="EO9" t="n">
-        <v>1.204963906431544e-11</v>
+        <v>1.029383911443915e-09</v>
       </c>
       <c r="EP9" t="n">
-        <v>4.556547500422781e-11</v>
+        <v>3.386975588881569e-09</v>
       </c>
       <c r="EQ9" t="n">
-        <v>6.572693084239134e-11</v>
+        <v>6.824274478844927e-11</v>
       </c>
       <c r="ER9" t="n">
-        <v>1.486013222196103e-11</v>
+        <v>5.685035775471192e-10</v>
       </c>
       <c r="ES9" t="n">
-        <v>1.571447416637284e-10</v>
+        <v>9.155979308062001e-10</v>
       </c>
       <c r="ET9" t="n">
-        <v>9.904656261827682e-11</v>
+        <v>7.291486303628858e-10</v>
       </c>
       <c r="EU9" t="n">
-        <v>3.591454911244796e-11</v>
+        <v>4.031292522022056e-10</v>
       </c>
       <c r="EV9" t="n">
-        <v>2.431566059613033e-10</v>
+        <v>1.743171829104995e-09</v>
       </c>
       <c r="EW9" t="n">
-        <v>5.636589112123502e-11</v>
+        <v>2.085107642102457e-09</v>
       </c>
       <c r="EX9" t="n">
-        <v>1.950769407121911e-12</v>
+        <v>3.829335182281568e-10</v>
       </c>
       <c r="EY9" t="n">
-        <v>6.565260834978659e-11</v>
+        <v>7.832291260001512e-09</v>
       </c>
       <c r="EZ9" t="n">
-        <v>5.217728679673961e-11</v>
+        <v>3.373784862592544e-10</v>
       </c>
       <c r="FA9" t="n">
-        <v>5.048866880130731e-11</v>
+        <v>3.702685935635941e-09</v>
       </c>
       <c r="FB9" t="n">
-        <v>3.554383523618476e-11</v>
+        <v>1.071377320194244e-09</v>
       </c>
       <c r="FC9" t="n">
-        <v>3.933339418060733e-11</v>
+        <v>3.716221108618356e-09</v>
       </c>
       <c r="FD9" t="n">
-        <v>2.492323188107992e-11</v>
+        <v>2.106026741888201e-10</v>
       </c>
       <c r="FE9" t="n">
-        <v>1.429514666362319e-11</v>
+        <v>2.548569133509204e-09</v>
       </c>
       <c r="FF9" t="n">
-        <v>9.126831235217736e-11</v>
+        <v>5.067250508083987e-10</v>
       </c>
       <c r="FG9" t="n">
-        <v>1.567744892239098e-11</v>
+        <v>4.827577226862445e-11</v>
       </c>
       <c r="FH9" t="n">
-        <v>7.312486033361765e-11</v>
+        <v>5.579868123106735e-09</v>
       </c>
       <c r="FI9" t="n">
-        <v>2.273336380254065e-10</v>
+        <v>4.598130765032238e-09</v>
       </c>
       <c r="FJ9" t="n">
-        <v>2.196531012632619e-10</v>
+        <v>4.599113090364426e-09</v>
       </c>
       <c r="FK9" t="n">
-        <v>5.857365287242899e-11</v>
+        <v>3.094717371254774e-09</v>
       </c>
       <c r="FL9" t="n">
-        <v>5.461565227848908e-11</v>
+        <v>5.594599450375881e-09</v>
       </c>
       <c r="FM9" t="n">
-        <v>1.903938985636788e-11</v>
+        <v>2.477401617184682e-09</v>
       </c>
       <c r="FN9" t="n">
-        <v>1.448881986609862e-10</v>
+        <v>3.228688427725501e-09</v>
       </c>
       <c r="FO9" t="n">
-        <v>1.024549056705126e-10</v>
+        <v>1.126156501385367e-08</v>
       </c>
       <c r="FP9" t="n">
-        <v>2.961580286564569e-11</v>
+        <v>6.00923044657975e-09</v>
       </c>
       <c r="FQ9" t="n">
-        <v>7.769096130316733e-12</v>
+        <v>1.099728041964454e-08</v>
       </c>
       <c r="FR9" t="n">
-        <v>1.503917684830824e-10</v>
+        <v>8.294386510954155e-09</v>
       </c>
       <c r="FS9" t="n">
-        <v>1.162105967011939e-10</v>
+        <v>2.180354341518864e-09</v>
       </c>
       <c r="FT9" t="n">
-        <v>2.161676809775415e-10</v>
+        <v>1.341037836333214e-09</v>
       </c>
       <c r="FU9" t="n">
-        <v>3.933279396628464e-11</v>
+        <v>4.363381878036421e-10</v>
       </c>
       <c r="FV9" t="n">
-        <v>4.106522760727316e-11</v>
+        <v>4.779711293423361e-09</v>
       </c>
       <c r="FW9" t="n">
-        <v>4.071639553293593e-11</v>
+        <v>1.031825291875066e-08</v>
       </c>
       <c r="FX9" t="n">
-        <v>1.249905734468371e-11</v>
+        <v>2.473848459416672e-09</v>
       </c>
       <c r="FY9" t="n">
-        <v>1.849008862686574e-10</v>
+        <v>1.697315399340482e-09</v>
       </c>
       <c r="FZ9" t="n">
-        <v>8.948097818262113e-11</v>
+        <v>2.048571756674278e-09</v>
       </c>
       <c r="GA9" t="n">
-        <v>3.471787440867402e-11</v>
+        <v>7.180507743953513e-09</v>
       </c>
       <c r="GB9" t="n">
-        <v>8.780149524101333e-11</v>
+        <v>1.305109131877202e-09</v>
       </c>
       <c r="GC9" t="n">
-        <v>1.880051947455996e-10</v>
+        <v>1.246911640606641e-08</v>
       </c>
       <c r="GD9" t="n">
-        <v>6.274966657393577e-11</v>
+        <v>9.527722610869205e-09</v>
       </c>
       <c r="GE9" t="n">
-        <v>2.989518632645627e-10</v>
+        <v>2.544945809646038e-09</v>
       </c>
       <c r="GF9" t="n">
-        <v>1.312299227618219e-12</v>
+        <v>1.526915927030359e-09</v>
       </c>
       <c r="GG9" t="n">
-        <v>1.18178106189859e-10</v>
+        <v>2.939986032401976e-09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0008215091074816883</v>
+        <v>2.361168299103156e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>0.007357816211879253</v>
+        <v>0.0005069130565971136</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0007596974610351026</v>
+        <v>0.0001795350108295679</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002901285421103239</v>
+        <v>0.0002098018449032679</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001185678644105792</v>
+        <v>1.854811853263527e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003822124563157558</v>
+        <v>0.0005148540949448943</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000451955886092037</v>
+        <v>4.986057319911197e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.002513336483389139</v>
+        <v>0.0002314954035682604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0008211316308006644</v>
+        <v>0.0001216529490193352</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00168187078088522</v>
+        <v>0.0001035200548358262</v>
       </c>
       <c r="K10" t="n">
-        <v>0.006597218103706837</v>
+        <v>0.0005949715850874782</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003580268821679056</v>
+        <v>0.0002499231486581266</v>
       </c>
       <c r="M10" t="n">
-        <v>0.002426447346806526</v>
+        <v>0.0004454495501704514</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0001952547172550112</v>
+        <v>0.0002209945232607424</v>
       </c>
       <c r="O10" t="n">
-        <v>0.003576611168682575</v>
+        <v>0.0006037885323166847</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0003313964116387069</v>
+        <v>4.679514313465916e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0006102535990066826</v>
+        <v>7.011048728600144e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001637006178498268</v>
+        <v>0.0001259000127902254</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0003023514873348176</v>
+        <v>0.0001028400292852893</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0007793501717969775</v>
+        <v>4.836438165511936e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>0.000668381922878325</v>
+        <v>6.479662260971963e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0004772191459778696</v>
+        <v>4.498981797951274e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0005813061725348234</v>
+        <v>9.0493616880849e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001130633638240397</v>
+        <v>0.0001262586301891133</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0004888223484158516</v>
+        <v>0.000115302660560701</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001270859269425273</v>
+        <v>0.0001290798682020977</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001157693914137781</v>
+        <v>7.350792293436825e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0004067051340825856</v>
+        <v>6.624336674576625e-05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0004819438909180462</v>
+        <v>2.709173713810742e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.651000638958067e-05</v>
+        <v>9.595199662726372e-05</v>
       </c>
       <c r="AE10" t="n">
-        <v>7.823276973795146e-05</v>
+        <v>0.0001256077375728637</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0008778382325544953</v>
+        <v>0.0001428814139217138</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0003365974698681384</v>
+        <v>0.0002142470475519076</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.000314327422529459</v>
+        <v>3.422261215746403e-05</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.000212902610655874</v>
+        <v>0.0003720480599440634</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0005985636962577701</v>
+        <v>2.369873436691705e-05</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0007691995706409216</v>
+        <v>9.070755913853645e-05</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.001172114629298449</v>
+        <v>6.020470027578995e-05</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0001489598944317549</v>
+        <v>5.082981078885496e-05</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0007968096761032939</v>
+        <v>8.072535274550319e-05</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0002859412925317883</v>
+        <v>0.0001110259108827449</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0009501046733930707</v>
+        <v>8.928793977247551e-05</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0005664450582116842</v>
+        <v>2.505390693841036e-05</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0001220673584612086</v>
+        <v>8.149011409841478e-05</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.001031357096508145</v>
+        <v>6.865069735795259e-06</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0005972487851977348</v>
+        <v>0.0001192790296045132</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.004268782213330269</v>
+        <v>0.0004193305503576994</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0003024619072675705</v>
+        <v>0.000161472344188951</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.000675296294502914</v>
+        <v>0.0001261488650925457</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0003070602251682431</v>
+        <v>0.0004223840369377285</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.003067437093704939</v>
+        <v>0.0004671081260312349</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.002042683074250817</v>
+        <v>1.783812695066445e-05</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.001134681515395641</v>
+        <v>8.002384856808931e-05</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.002112460788339376</v>
+        <v>1.033380976878107e-05</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0005722347996197641</v>
+        <v>0.0001262123550986871</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.00128172873519361</v>
+        <v>2.683610728126951e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.001583439647220075</v>
+        <v>0.0001276154507650062</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0002794331812765449</v>
+        <v>0.0001322798780165613</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0008011817699298263</v>
+        <v>0.0002016730722971261</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0005111470818519592</v>
+        <v>6.226840196177363e-05</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.000876224716193974</v>
+        <v>4.01230608986225e-05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.00128467008471489</v>
+        <v>0.0002573454694356769</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.001478591118939221</v>
+        <v>6.507713987957686e-05</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0002639266895130277</v>
+        <v>2.632092946441844e-05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0007923795492388308</v>
+        <v>0.0001428815448889509</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0007976455963216722</v>
+        <v>5.200373561820015e-05</v>
       </c>
       <c r="BO10" t="n">
-        <v>6.533224950544536e-05</v>
+        <v>9.874247189145535e-05</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0001940045331139117</v>
+        <v>0.0001209231413668022</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0005466399015858769</v>
+        <v>7.09518208168447e-05</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0008900591637939215</v>
+        <v>9.490567026659846e-05</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0007337903371080756</v>
+        <v>8.161296136677265e-05</v>
       </c>
       <c r="BT10" t="n">
-        <v>3.813314833678305e-05</v>
+        <v>8.107542817015201e-05</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.08155722450465e-06</v>
+        <v>7.68398167565465e-05</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.002433221088722348</v>
+        <v>0.0001625911827431992</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.001224022707901895</v>
+        <v>3.023509634658694e-06</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0002091674832627177</v>
+        <v>4.858869942836463e-06</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0005235119024291635</v>
+        <v>3.40317128575407e-05</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.001480267150327563</v>
+        <v>0.000246440147748217</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0003995225997641683</v>
+        <v>0.000181739596882835</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0003558454918675125</v>
+        <v>5.946312376181595e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0009209542768076062</v>
+        <v>9.500309533905238e-05</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0001468190748710185</v>
+        <v>1.288792736886535e-05</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.001312564476393163</v>
+        <v>0.0001655761443544179</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0006458446732722223</v>
+        <v>5.597477138508111e-05</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0001545480045024306</v>
+        <v>4.660504782805219e-05</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0002390662557445467</v>
+        <v>4.7318622819148e-05</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0003412157238926739</v>
+        <v>0.0001290224900003523</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.000555011909455061</v>
+        <v>9.572506314725615e-06</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0005050198524259031</v>
+        <v>2.894245517381933e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0006179085467010736</v>
+        <v>5.926540325162932e-07</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.001559398369863629</v>
+        <v>6.446013867389411e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0002937455428764224</v>
+        <v>5.944474833086133e-05</v>
       </c>
       <c r="CO10" t="n">
-        <v>3.583227953640744e-05</v>
+        <v>0.0001833692804211751</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.002599035855382681</v>
+        <v>0.000131472508655861</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0006276926142163575</v>
+        <v>8.936096855904907e-05</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0009578306926414371</v>
+        <v>5.406925993156619e-05</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.00154670502524823</v>
+        <v>0.0001602765842108056</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.001143148168921471</v>
+        <v>0.000236167325056158</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0004399843164719641</v>
+        <v>0.0001049040656653233</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0001482634979765862</v>
+        <v>5.488972965395078e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.001282103592529893</v>
+        <v>0.000141042226459831</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0006782902637496591</v>
+        <v>7.862330676289275e-05</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0005645649507641792</v>
+        <v>7.207577436929569e-05</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0003633728192653507</v>
+        <v>5.295799928717315e-05</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0002311684074811637</v>
+        <v>0.0001679480192251503</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0005277460440993309</v>
+        <v>2.975814277306199e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0008844244293868542</v>
+        <v>3.088625817326829e-05</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0005930714542046189</v>
+        <v>9.534956916468218e-06</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0008343485533259809</v>
+        <v>1.014861663861666e-05</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0006092777475714684</v>
+        <v>0.0001996315259020776</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0004233690269757062</v>
+        <v>0.0001691967772785574</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.001156477024778724</v>
+        <v>0.0001031243882607669</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001250251661986113</v>
+        <v>2.946358472399879e-05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.003813724033534527</v>
+        <v>0.0001469608250772581</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0006673276657238603</v>
+        <v>1.592321677890141e-05</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001813372480683029</v>
+        <v>0.0002006993163377047</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.001558636082336307</v>
+        <v>4.118921788176522e-05</v>
       </c>
       <c r="DN10" t="n">
-        <v>2.334002056159079e-05</v>
+        <v>5.153475649422035e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0006259322399273515</v>
+        <v>0.0001198892714455724</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0007168910815380514</v>
+        <v>3.115959771093912e-05</v>
       </c>
       <c r="DQ10" t="n">
-        <v>4.751826782012358e-05</v>
+        <v>0.0001183942731586285</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0004305627080611885</v>
+        <v>6.550193575094454e-06</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.001276345225051045</v>
+        <v>9.324280836153775e-05</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.001376683358103037</v>
+        <v>0.000108953652670607</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.000288891838863492</v>
+        <v>0.0002086389577016234</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0001010065025184304</v>
+        <v>8.024144335649908e-05</v>
       </c>
       <c r="DW10" t="n">
-        <v>6.435421528294683e-05</v>
+        <v>9.370094630867243e-06</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0007772127282805741</v>
+        <v>5.969551421003416e-05</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.000683779246173799</v>
+        <v>0.000173809879925102</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.001013372908346355</v>
+        <v>3.559144715836737e-06</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0004152124165557325</v>
+        <v>0.0001500970683991909</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.000545650371350348</v>
+        <v>2.175756162614562e-05</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0004468656843528152</v>
+        <v>0.0001604059507371858</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0001848116371547803</v>
+        <v>0.0001592575281392783</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.001598475617356598</v>
+        <v>0.0001985089620575309</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0005698305321857333</v>
+        <v>1.529207656858489e-05</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.001432370045222342</v>
+        <v>1.874964073067531e-05</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.0005487552843987942</v>
+        <v>2.974247763631865e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0003158509207423776</v>
+        <v>5.237366349319927e-05</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.000407946587074548</v>
+        <v>4.416456795297563e-05</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.001170337316580117</v>
+        <v>4.906339017907158e-05</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0009162219939753413</v>
+        <v>3.75697563868016e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0003119456523563713</v>
+        <v>2.771158688119613e-05</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0002561459550634027</v>
+        <v>0.0001035262685036287</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0001874671434052289</v>
+        <v>5.508178946911357e-05</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0008519500261172652</v>
+        <v>0.0001177641388494521</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0009522722102701664</v>
+        <v>7.061517680995166e-05</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0003711887402459979</v>
+        <v>0.0001281744334846735</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.001207914901897311</v>
+        <v>6.693473551422358e-05</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0005253757699392736</v>
+        <v>0.0001364735799143091</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.001730679767206311</v>
+        <v>2.924345608334988e-06</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.001975083723664284</v>
+        <v>3.99424388888292e-05</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0003197209734935313</v>
+        <v>2.414841765130404e-05</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0003268037107773125</v>
+        <v>4.036410973640159e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.001200464088469744</v>
+        <v>0.000181354145752266</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0005563810700550675</v>
+        <v>4.441983764991164e-05</v>
       </c>
       <c r="FA10" t="n">
-        <v>1.240198616869748e-05</v>
+        <v>9.121783659793437e-05</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0002984690072480589</v>
+        <v>4.217864261590876e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0001476836914662272</v>
+        <v>0.0001293058594455943</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0009641296928748488</v>
+        <v>1.555617927806452e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0007885682862251997</v>
+        <v>2.631771531014238e-05</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0008531216299161315</v>
+        <v>3.487666617729701e-05</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0002685680228751153</v>
+        <v>9.244085958926007e-06</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0004212309431750327</v>
+        <v>7.253210060298443e-05</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.001085583702661097</v>
+        <v>0.0001024126977426931</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.001376043073832989</v>
+        <v>0.0001129777883761562</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0004222843563184142</v>
+        <v>1.84786222234834e-05</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0004832374979741871</v>
+        <v>0.0001790795067790896</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0005190055817365646</v>
+        <v>4.13148918596562e-05</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.000526027986779809</v>
+        <v>0.000123851903481409</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0008158473065122962</v>
+        <v>0.0002751050051301718</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0008496994851157069</v>
+        <v>0.0001100521330954507</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0001778975711204112</v>
+        <v>0.0001060959839378484</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0007066731341183186</v>
+        <v>1.917616464197636e-05</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.001005546771921217</v>
+        <v>7.538063800893724e-05</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0004911533906124532</v>
+        <v>4.125521081732586e-05</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001013282453641295</v>
+        <v>5.533142029889859e-05</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.001066962257027626</v>
+        <v>0.0001398139720549807</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.000961143639869988</v>
+        <v>0.0004502097144722939</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0006661137449555099</v>
+        <v>9.299379598814994e-06</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.001504588406533003</v>
+        <v>6.750159082002938e-05</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0005232733092270792</v>
+        <v>9.309287997893989e-05</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0005885412101633847</v>
+        <v>0.0002356324694119394</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0002604089095257223</v>
+        <v>4.595626523951069e-05</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0009951444808393717</v>
+        <v>0.0002855887578334659</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0004141477693337947</v>
+        <v>0.0001653600193094462</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.001735927420668304</v>
+        <v>5.797818448627368e-05</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0005707900272682309</v>
+        <v>5.293959839036688e-05</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0002111555077135563</v>
+        <v>1.0623922207742e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.01861057803034782</v>
+        <v>7.691685459576547e-05</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2371256947517395</v>
+        <v>0.0003072718100156635</v>
       </c>
       <c r="C11" t="n">
-        <v>0.006445686332881451</v>
+        <v>8.086328307399526e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1187348589301109</v>
+        <v>0.000139282681629993</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0323340892791748</v>
+        <v>2.964583836728707e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.203238770365715</v>
+        <v>0.0002460949181113392</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001469207927584648</v>
+        <v>7.335331611102447e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08297643065452576</v>
+        <v>5.382629024097696e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01685802266001701</v>
+        <v>2.620859049784485e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04856201261281967</v>
+        <v>6.06481044087559e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2230824679136276</v>
+        <v>0.0003722988767549396</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004515244159847498</v>
+        <v>3.619294875534251e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>0.08597143739461899</v>
+        <v>0.0002394993061898276</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003100891131907701</v>
+        <v>0.0001041201467160136</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1893228590488434</v>
+        <v>0.0003065447090193629</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01312901824712753</v>
+        <v>1.62144388013985e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03677046671509743</v>
+        <v>5.395979678723961e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.005585072096437216</v>
+        <v>5.801376391900703e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01078718341886997</v>
+        <v>2.669899913598783e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01615801453590393</v>
+        <v>3.404895687708631e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02153419330716133</v>
+        <v>3.690987796289846e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>0.03197560459375381</v>
+        <v>3.376134191057645e-05</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0583316832780838</v>
+        <v>1.433596480637789e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0186696108430624</v>
+        <v>4.896780956187285e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01893303729593754</v>
+        <v>3.684147304738872e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.05739665031433105</v>
+        <v>0.0001411184493917972</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.03486910462379456</v>
+        <v>8.815244655124843e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001438789069652557</v>
+        <v>6.378634134307504e-05</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0133759044110775</v>
+        <v>3.182239743182436e-05</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.009325931780040264</v>
+        <v>2.891817348427139e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.009861024096608162</v>
+        <v>7.368098886217922e-05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01389772724360228</v>
+        <v>7.501863001380116e-05</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0143308974802494</v>
+        <v>9.57558659138158e-05</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.01284622400999069</v>
+        <v>1.038577920553507e-05</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.008509773761034012</v>
+        <v>0.0002094470110023394</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0130384424701333</v>
+        <v>3.103895505773835e-05</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.02094356715679169</v>
+        <v>7.265630119945854e-05</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.04187099635601044</v>
+        <v>3.806336462730542e-05</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.002297541126608849</v>
+        <v>3.82097132387571e-05</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.008399352431297302</v>
+        <v>3.109603494522162e-05</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0009102043695747852</v>
+        <v>3.698737600643653e-06</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.02807123400270939</v>
+        <v>4.573251771944342e-06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.00256158341653645</v>
+        <v>3.918401489499956e-05</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.01317024976015091</v>
+        <v>0.000139212075737305</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.02483553253114223</v>
+        <v>2.128598316630814e-05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.03235190361738205</v>
+        <v>0.0001164827408501878</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1736998409032822</v>
+        <v>0.0002425203565508127</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.005375235341489315</v>
+        <v>6.464351463364437e-05</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.04496053233742714</v>
+        <v>6.902298628119752e-05</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.01709465309977531</v>
+        <v>0.0001876322639873251</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.1077655255794525</v>
+        <v>0.0001726334303384647</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.02394679933786392</v>
+        <v>5.942084499110933e-06</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0204777829349041</v>
+        <v>8.392642484977841e-06</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.06129929423332214</v>
+        <v>4.703050944954157e-05</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0216589942574501</v>
+        <v>1.221837555931415e-05</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03791249915957451</v>
+        <v>5.933384090894833e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.04754414781928062</v>
+        <v>1.650933700148016e-05</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.00249142711982131</v>
+        <v>0.0001169502138509415</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.03823554515838623</v>
+        <v>7.435803854605183e-05</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.06128839775919914</v>
+        <v>5.427400537882932e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.01917595602571964</v>
+        <v>2.736876922426745e-05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.01999368704855442</v>
+        <v>8.326924580615014e-05</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.01394461281597614</v>
+        <v>5.294046422932297e-05</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.0001503666862845421</v>
+        <v>1.321857234870549e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0546487532556057</v>
+        <v>3.645935066742823e-05</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.00672224722802639</v>
+        <v>1.886590212052397e-06</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.01508929952979088</v>
+        <v>6.962921179365367e-05</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.003939978778362274</v>
+        <v>2.317588041478302e-05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.001912229578010738</v>
+        <v>1.05286089819856e-05</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.01697306707501411</v>
+        <v>0.000124360216432251</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.006471746601164341</v>
+        <v>1.833459464251064e-05</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.006727925501763821</v>
+        <v>8.065887232078239e-05</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.01539248321205378</v>
+        <v>3.784135333262384e-05</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.09007550776004791</v>
+        <v>0.0001345257624052465</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.01483060978353024</v>
+        <v>2.049492104561068e-05</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.03765137121081352</v>
+        <v>6.383928848663345e-05</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.02255133725702763</v>
+        <v>3.248325811000541e-06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.04176545515656471</v>
+        <v>8.927455201046541e-05</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.01393814291805029</v>
+        <v>3.400472633074969e-05</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0002313493750989437</v>
+        <v>2.527182368794456e-05</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.04003608599305153</v>
+        <v>4.524458199739456e-05</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.001381583511829376</v>
+        <v>1.066539516614284e-05</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.03101350367069244</v>
+        <v>9.209743438987061e-05</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.02275220118463039</v>
+        <v>3.784714863286354e-06</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.01631583645939827</v>
+        <v>3.520170139381662e-05</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.005913358181715012</v>
+        <v>1.502861596236471e-05</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0315823070704937</v>
+        <v>8.074149081949145e-05</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.01641953736543655</v>
+        <v>2.530566962377634e-05</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.01131806336343288</v>
+        <v>1.880705167423002e-05</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.02083336561918259</v>
+        <v>3.772290074266493e-05</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.05034342035651207</v>
+        <v>3.250980807933956e-05</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.007730855606496334</v>
+        <v>9.80980257736519e-05</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.005318635143339634</v>
+        <v>8.703589264769107e-05</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0362873338162899</v>
+        <v>0.0001225228043040261</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.001192907337099314</v>
+        <v>2.261467670905404e-06</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.006107674911618233</v>
+        <v>8.500288822688162e-05</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.04923717677593231</v>
+        <v>5.848703949595802e-06</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.04619910195469856</v>
+        <v>0.0001025323872454464</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.009500612504780293</v>
+        <v>3.769935574382544e-05</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0001195187214761972</v>
+        <v>2.348103953409009e-05</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.02730012498795986</v>
+        <v>8.889888704288751e-05</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.01881650649011135</v>
+        <v>1.058936959452694e-06</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.02870979718863964</v>
+        <v>5.380349466577172e-05</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.007997095584869385</v>
+        <v>1.63135991897434e-05</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.03324554488062859</v>
+        <v>8.741121564526111e-05</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.01652374491095543</v>
+        <v>5.449879608931951e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.02352634444832802</v>
+        <v>2.382257298449986e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.01090287044644356</v>
+        <v>3.269608714617789e-05</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.005340783856809139</v>
+        <v>2.506393684598152e-05</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.01120668277144432</v>
+        <v>5.012480323784985e-05</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.007310524582862854</v>
+        <v>4.254374653100967e-05</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.08527781814336777</v>
+        <v>1.193059233628446e-05</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.04483778774738312</v>
+        <v>0.0001924586395034567</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02795918844640255</v>
+        <v>8.084376895567402e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.004713171161711216</v>
+        <v>5.913638233323582e-05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.03878370299935341</v>
+        <v>1.742140739224851e-06</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.02164205349981785</v>
+        <v>2.927568857558072e-06</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.004920377396047115</v>
+        <v>3.202759035048075e-05</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0031406763009727</v>
+        <v>6.178076728247106e-05</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.01693795807659626</v>
+        <v>1.819178214645945e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0004337313584983349</v>
+        <v>5.311001586960629e-05</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.008421801961958408</v>
+        <v>2.330850657017436e-05</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.002283880952745676</v>
+        <v>2.551390934968367e-05</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.00104664801619947</v>
+        <v>5.983177834423259e-05</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.002834649290889502</v>
+        <v>0.0001228998880833387</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.02057269774377346</v>
+        <v>4.802750481758267e-05</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0001513669267296791</v>
+        <v>3.133450445602648e-05</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0252188928425312</v>
+        <v>1.87354235094972e-05</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.01928079500794411</v>
+        <v>3.274233677075244e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.008103316649794579</v>
+        <v>4.372009425424039e-05</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.00138934375718236</v>
+        <v>6.830459460616112e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.01551226247102022</v>
+        <v>4.313945100875571e-05</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0007104217074811459</v>
+        <v>3.700749584822915e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.004836912266910076</v>
+        <v>6.078441219870001e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0101972296833992</v>
+        <v>7.395865395665169e-05</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.01348243094980717</v>
+        <v>2.134999022018746e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.03572700917720795</v>
+        <v>2.157592825824395e-05</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.01130735781043768</v>
+        <v>3.755558282136917e-05</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.007187223993241787</v>
+        <v>1.986643837881275e-06</v>
       </c>
       <c r="EJ11" t="n">
-        <v>8.202483877539635e-05</v>
+        <v>1.140911626862362e-05</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.02313658222556114</v>
+        <v>2.899988248827867e-05</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.01592731103301048</v>
+        <v>1.62789237947436e-05</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.006859187036752701</v>
+        <v>6.775162091798848e-06</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.01097701955586672</v>
+        <v>1.743659959174693e-05</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.001153502613306046</v>
+        <v>3.267017018515617e-05</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01492869574576616</v>
+        <v>4.102702951058745e-05</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.01754457503557205</v>
+        <v>4.007309325970709e-05</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.02199815027415752</v>
+        <v>4.721219738712534e-05</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01740813255310059</v>
+        <v>4.862611240241677e-05</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.02959133125841618</v>
+        <v>6.817911344114691e-05</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.03905221074819565</v>
+        <v>2.747707912931219e-05</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.06678984314203262</v>
+        <v>4.716587864095345e-05</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.005901198834180832</v>
+        <v>4.893737786915153e-05</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.004123020451515913</v>
+        <v>2.409339685982559e-05</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.02567833662033081</v>
+        <v>0.0001116581843234599</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0155309671536088</v>
+        <v>1.008548451864044e-06</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.02027012594044209</v>
+        <v>6.7401364503894e-05</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.004942032974213362</v>
+        <v>3.361576091265306e-05</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02759478241205215</v>
+        <v>6.965905777178705e-05</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.02859637886285782</v>
+        <v>1.932503073476255e-05</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.01527217030525208</v>
+        <v>2.0131274141022e-05</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.02188032492995262</v>
+        <v>1.615869223314803e-05</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.01078008860349655</v>
+        <v>2.069177753583062e-05</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.007210119161754847</v>
+        <v>0.0001290930085815489</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.01567903906106949</v>
+        <v>7.44444114388898e-05</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.03749755769968033</v>
+        <v>9.857016993919387e-05</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.008984709158539772</v>
+        <v>4.490958963287994e-05</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01825453341007233</v>
+        <v>0.0001205470762215555</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.0005547641776502132</v>
+        <v>1.38623763632495e-05</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.01815658807754517</v>
+        <v>7.851590635254979e-05</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.01698459312319756</v>
+        <v>6.700785888824612e-05</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.01559801958501339</v>
+        <v>1.580220487085171e-05</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.03934814780950546</v>
+        <v>3.913992986781523e-05</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.03251191973686218</v>
+        <v>0.0001950183359440416</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0003659832291305065</v>
+        <v>3.248353459639475e-05</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.004876871593296528</v>
+        <v>0.0001110694793169387</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01117378659546375</v>
+        <v>1.0976964404108e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.02655639685690403</v>
+        <v>3.012898014276288e-05</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.004022484645247459</v>
+        <v>2.379688339715358e-05</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.01491651218384504</v>
+        <v>1.347186116618104e-05</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.04654818028211594</v>
+        <v>1.862807766883634e-05</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.01586588658392429</v>
+        <v>6.941500760149211e-05</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.02829737588763237</v>
+        <v>6.398886034730822e-05</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.01245159562677145</v>
+        <v>1.255087590834592e-05</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.01304948329925537</v>
+        <v>0.0001825021317927167</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.01801168918609619</v>
+        <v>8.525674638804048e-05</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1004845723509789</v>
+        <v>2.506627606635448e-05</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.001938051544129848</v>
+        <v>3.56614327756688e-05</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.004058975260704756</v>
+        <v>2.736289025051519e-05</v>
       </c>
     </row>
     <row r="12">
@@ -7827,1140 +7827,1140 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.000144314777571708</v>
+        <v>9.684785027275211e-07</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001869396190159023</v>
+        <v>5.619906914944295e-06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001237125543411821</v>
+        <v>4.913781594950706e-07</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000392859656130895</v>
+        <v>1.713130131975049e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004673385119531304</v>
+        <v>2.78321499536105e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0004175872600171715</v>
+        <v>8.052302291616797e-06</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000289405114017427</v>
+        <v>2.796407898131292e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0002337529003852978</v>
+        <v>5.58515966986306e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0002795870532281697</v>
+        <v>5.080403298052261e-07</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0002041987463599071</v>
+        <v>5.367971880332334e-07</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001648076227866113</v>
+        <v>6.849195415270515e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>4.456980605027638e-06</v>
+        <v>2.680597390281036e-06</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0002343781525269151</v>
+        <v>4.080195594724501e-06</v>
       </c>
       <c r="N14" t="n">
-        <v>7.928599370643497e-05</v>
+        <v>6.673756161035271e-06</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0003300730313640088</v>
+        <v>1.065810465661343e-05</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001585933787282556</v>
+        <v>1.781623495844542e-06</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0001919291680678725</v>
+        <v>3.687071966851363e-06</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0003656261833384633</v>
+        <v>1.2646103186853e-07</v>
       </c>
       <c r="S14" t="n">
-        <v>8.659066224936396e-05</v>
+        <v>1.97168361637523e-08</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0002210674429079518</v>
+        <v>4.724053042082232e-07</v>
       </c>
       <c r="U14" t="n">
-        <v>6.789417966501787e-05</v>
+        <v>1.110426183004165e-06</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0001651412167120725</v>
+        <v>6.557239657922764e-07</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0002051943447440863</v>
+        <v>9.018548894346168e-07</v>
       </c>
       <c r="X14" t="n">
-        <v>6.040728112566285e-05</v>
+        <v>1.340832113783108e-06</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.820397821778897e-05</v>
+        <v>8.903189154807478e-07</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0003487916255835444</v>
+        <v>2.789565314742504e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0001241104037035257</v>
+        <v>7.29408384358976e-07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.000136229646159336</v>
+        <v>1.666501248109853e-06</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0001441746426280588</v>
+        <v>1.679826482359204e-07</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.813095877878368e-05</v>
+        <v>1.801201676698838e-07</v>
       </c>
       <c r="AE14" t="n">
-        <v>9.937054710462689e-05</v>
+        <v>2.139785920007853e-06</v>
       </c>
       <c r="AF14" t="n">
-        <v>6.070603194530122e-05</v>
+        <v>1.874179702099354e-06</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.553246955969371e-05</v>
+        <v>1.961207090062089e-06</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.011488974560052e-05</v>
+        <v>3.803770027843711e-07</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.951438263058662e-05</v>
+        <v>4.753524990519509e-06</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4.024465306429192e-05</v>
+        <v>1.498428218837944e-06</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0003018919960595667</v>
+        <v>7.092679084053088e-07</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0001816431031329557</v>
+        <v>1.90117475540319e-07</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.401021604076959e-05</v>
+        <v>1.454897073926986e-07</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0001500809448771179</v>
+        <v>3.587396406601329e-07</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0001624881697352976</v>
+        <v>1.036801222653594e-06</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.00012848453479819</v>
+        <v>6.078618071114761e-07</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0001283932651858777</v>
+        <v>2.119687110280211e-07</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.588609666214325e-05</v>
+        <v>2.395747287664562e-06</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0001367280056001619</v>
+        <v>3.810362727563188e-07</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.662845119833946e-05</v>
+        <v>1.187052134810074e-06</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.001121829729527235</v>
+        <v>7.045618986012414e-06</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.0001618846436031163</v>
+        <v>9.731909358379198e-07</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.812497981125489e-05</v>
+        <v>9.906088962452486e-07</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.229076436487958e-05</v>
+        <v>3.979099801654229e-06</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0001172524498542771</v>
+        <v>6.843269147793762e-06</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0004197589005343616</v>
+        <v>4.955153372065979e-07</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0001679434790275991</v>
+        <v>2.002920837185229e-06</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0001625605946173891</v>
+        <v>6.427679863918456e-07</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.578893665689975e-05</v>
+        <v>6.186841119415476e-07</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0002903149579651654</v>
+        <v>1.137914978244225e-06</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0002992796071339399</v>
+        <v>1.311314008489717e-06</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.877493721432984e-05</v>
+        <v>2.303259634572896e-06</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.000282326975138858</v>
+        <v>1.731100155666354e-06</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0002185789489885792</v>
+        <v>1.686076274154402e-07</v>
       </c>
       <c r="BI14" t="n">
-        <v>5.221756873652339e-05</v>
+        <v>7.477868848582148e-07</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0002228934463346377</v>
+        <v>4.259712113707792e-06</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0003162974899169058</v>
+        <v>4.206711423648812e-08</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001090959849534556</v>
+        <v>7.330048390485899e-08</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0001654686639085412</v>
+        <v>2.32239881370333e-06</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.707854895968921e-05</v>
+        <v>7.285259471245809e-07</v>
       </c>
       <c r="BO14" t="n">
-        <v>8.407361747231334e-05</v>
+        <v>1.977221018023556e-06</v>
       </c>
       <c r="BP14" t="n">
-        <v>8.476828952552751e-05</v>
+        <v>1.441351173525618e-06</v>
       </c>
       <c r="BQ14" t="n">
-        <v>2.976757787109818e-05</v>
+        <v>8.206473012251081e-07</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0001225361338583753</v>
+        <v>1.970964149222709e-06</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.372489143454004e-05</v>
+        <v>1.100851250157575e-06</v>
       </c>
       <c r="BT14" t="n">
-        <v>8.294339932035655e-05</v>
+        <v>1.889286750156316e-06</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.47357417922467e-05</v>
+        <v>2.328087873593176e-07</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0006513716070912778</v>
+        <v>3.262189466113341e-06</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0001497179036960006</v>
+        <v>7.506096153520048e-07</v>
       </c>
       <c r="BX14" t="n">
-        <v>8.579660061514005e-05</v>
+        <v>1.223093363478256e-06</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.057842594804242e-05</v>
+        <v>1.550179490550363e-06</v>
       </c>
       <c r="BZ14" t="n">
-        <v>8.509851795679424e-06</v>
+        <v>3.292037717983476e-06</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.072478234069422e-05</v>
+        <v>5.93773108903406e-07</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.524679414113052e-06</v>
+        <v>1.619275508346618e-06</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.377466029836796e-05</v>
+        <v>3.921083191471553e-08</v>
       </c>
       <c r="CD14" t="n">
-        <v>8.167060877894983e-05</v>
+        <v>6.817296593908395e-08</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0003189050767105073</v>
+        <v>1.539155846330686e-06</v>
       </c>
       <c r="CF14" t="n">
-        <v>6.631863652728498e-05</v>
+        <v>3.818142886302667e-07</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.623439235729165e-05</v>
+        <v>9.637009270591079e-07</v>
       </c>
       <c r="CH14" t="n">
-        <v>6.810612831031904e-05</v>
+        <v>8.825053328109789e-07</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.166157835541526e-05</v>
+        <v>2.222833472842467e-06</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0001224772859131917</v>
+        <v>6.137962600405444e-07</v>
       </c>
       <c r="CK14" t="n">
-        <v>5.08287557750009e-05</v>
+        <v>3.518284188430698e-07</v>
       </c>
       <c r="CL14" t="n">
-        <v>8.686283399583772e-05</v>
+        <v>8.774790671850496e-07</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0004538365465123206</v>
+        <v>5.230546662460256e-08</v>
       </c>
       <c r="CN14" t="n">
-        <v>6.880261935293674e-05</v>
+        <v>3.010694854310714e-06</v>
       </c>
       <c r="CO14" t="n">
-        <v>7.271065260283649e-05</v>
+        <v>2.52499125963368e-06</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0005464509013108909</v>
+        <v>4.111414909857558e-06</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0003382407012395561</v>
+        <v>7.907331109890947e-07</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0004243392031639814</v>
+        <v>1.965241608559154e-06</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0003089748206548393</v>
+        <v>5.525971573661081e-07</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0001630076149012893</v>
+        <v>1.867475816652586e-06</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0002466056030243635</v>
+        <v>4.395261328227207e-07</v>
       </c>
       <c r="CV14" t="n">
-        <v>7.479024498024955e-05</v>
+        <v>2.268551355655291e-07</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0003035457921214402</v>
+        <v>1.296880554946256e-06</v>
       </c>
       <c r="CX14" t="n">
-        <v>6.857843982288614e-05</v>
+        <v>4.113815634809725e-07</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0001324387994827703</v>
+        <v>1.352280833089026e-06</v>
       </c>
       <c r="CZ14" t="n">
-        <v>9.321765537606552e-05</v>
+        <v>9.975418606700259e-07</v>
       </c>
       <c r="DA14" t="n">
-        <v>3.159762491122819e-05</v>
+        <v>2.628138872751151e-06</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0001223819999722764</v>
+        <v>1.381135206202089e-09</v>
       </c>
       <c r="DC14" t="n">
-        <v>9.424450399819762e-05</v>
+        <v>2.94321893079541e-07</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.0001018870752886869</v>
+        <v>5.485295559992664e-07</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0001602504344191402</v>
+        <v>3.065380838052079e-07</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0002697846502996981</v>
+        <v>2.980675617436646e-06</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0001060251670423895</v>
+        <v>1.428810946890735e-06</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0002537966065574437</v>
+        <v>9.656830002313654e-08</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0005414252518676221</v>
+        <v>1.950915248016827e-06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0007134765619412065</v>
+        <v>2.240873754999484e-06</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.012119411025196e-05</v>
+        <v>8.315998911712086e-07</v>
       </c>
       <c r="DL14" t="n">
-        <v>9.285258420277387e-05</v>
+        <v>4.079189466210664e-07</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0004017963947262615</v>
+        <v>8.594325890953769e-07</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0001132622419390827</v>
+        <v>4.153641555149079e-07</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0001103864924516529</v>
+        <v>2.482081811194803e-07</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0001525800325907767</v>
+        <v>5.82933012083231e-07</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0001601546246092767</v>
+        <v>5.600585382126155e-07</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.784319313941523e-05</v>
+        <v>3.761632569876383e-07</v>
       </c>
       <c r="DS14" t="n">
-        <v>8.210854139178991e-05</v>
+        <v>1.434299576885678e-07</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0002380119840381667</v>
+        <v>1.502299028288689e-06</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0001968070573639125</v>
+        <v>2.710315811782493e-06</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0001036545509123243</v>
+        <v>4.086997762442479e-07</v>
       </c>
       <c r="DW14" t="n">
-        <v>4.389646710478701e-05</v>
+        <v>4.012409817732987e-07</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0002336534962523729</v>
+        <v>5.699266125702707e-07</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.561427289852872e-05</v>
+        <v>7.213426442831405e-07</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0002411552704870701</v>
+        <v>2.286475819346379e-06</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.000179271912202239</v>
+        <v>1.259161081179627e-06</v>
       </c>
       <c r="EB14" t="n">
-        <v>6.672294693998992e-05</v>
+        <v>1.215090833284194e-06</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.868046042043716e-05</v>
+        <v>6.004449915053556e-08</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0001862592907855287</v>
+        <v>1.30082480609417e-06</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0003856640250887722</v>
+        <v>2.496816705388483e-06</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0002549297641962767</v>
+        <v>1.703787262385958e-07</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0004440037009771913</v>
+        <v>7.792694418640167e-07</v>
       </c>
       <c r="EH14" t="n">
-        <v>2.573709934949875e-05</v>
+        <v>7.194722684289445e-07</v>
       </c>
       <c r="EI14" t="n">
-        <v>1.034650631481782e-05</v>
+        <v>5.608408741863968e-07</v>
       </c>
       <c r="EJ14" t="n">
-        <v>4.685897238232428e-06</v>
+        <v>9.080452514353965e-07</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0002432379842502996</v>
+        <v>1.606322939551319e-06</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.000168841754202731</v>
+        <v>5.279367201183049e-07</v>
       </c>
       <c r="EM14" t="n">
-        <v>9.037042764248326e-05</v>
+        <v>3.415898675029894e-07</v>
       </c>
       <c r="EN14" t="n">
-        <v>2.785430297080893e-05</v>
+        <v>1.324608405184335e-07</v>
       </c>
       <c r="EO14" t="n">
-        <v>8.689709648024291e-05</v>
+        <v>4.805992261935899e-07</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0001167322843684815</v>
+        <v>2.043582526312093e-06</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0001265308383153751</v>
+        <v>1.157423412223579e-06</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0001812790287658572</v>
+        <v>6.484280561380729e-07</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0001911258441396058</v>
+        <v>2.65766459506267e-07</v>
       </c>
       <c r="ET14" t="n">
-        <v>1.449551928089932e-05</v>
+        <v>1.72747377291671e-06</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.000333867414155975</v>
+        <v>9.894220056594349e-07</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0002429642336210236</v>
+        <v>3.351842678966932e-07</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0001060033100657165</v>
+        <v>6.103690566305886e-07</v>
       </c>
       <c r="EX14" t="n">
-        <v>9.93850699160248e-05</v>
+        <v>2.63361073393753e-07</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0003124684153590351</v>
+        <v>2.125008450093446e-06</v>
       </c>
       <c r="EZ14" t="n">
-        <v>5.056027293903753e-05</v>
+        <v>1.711809005655596e-07</v>
       </c>
       <c r="FA14" t="n">
-        <v>2.398886499577202e-05</v>
+        <v>1.616353529243497e-06</v>
       </c>
       <c r="FB14" t="n">
-        <v>6.406837928807363e-05</v>
+        <v>7.178064151958097e-07</v>
       </c>
       <c r="FC14" t="n">
-        <v>9.515457350062206e-06</v>
+        <v>2.286097696924116e-06</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0001864988298621029</v>
+        <v>5.653748758049915e-07</v>
       </c>
       <c r="FE14" t="n">
-        <v>7.94623265392147e-05</v>
+        <v>1.38033925622949e-07</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0001460718340240419</v>
+        <v>1.819516910472885e-07</v>
       </c>
       <c r="FG14" t="n">
-        <v>9.368343307869509e-05</v>
+        <v>1.619992673340676e-07</v>
       </c>
       <c r="FH14" t="n">
-        <v>9.774856880540028e-05</v>
+        <v>1.995362936213496e-06</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0001715690596029162</v>
+        <v>1.335662318524555e-06</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0002771826984826475</v>
+        <v>1.018633497551491e-06</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0001200075348606333</v>
+        <v>2.397688149358146e-06</v>
       </c>
       <c r="FL14" t="n">
-        <v>3.753237979253754e-05</v>
+        <v>2.278970214319997e-06</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0001360860042041168</v>
+        <v>1.277662249776768e-06</v>
       </c>
       <c r="FN14" t="n">
-        <v>7.71599734434858e-05</v>
+        <v>1.766970285643765e-06</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0001498602796345949</v>
+        <v>2.901727384596597e-06</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0002710186818148941</v>
+        <v>5.705722969651106e-07</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0001263443264178932</v>
+        <v>5.009051733395609e-07</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0002092294016620144</v>
+        <v>2.896080559366965e-06</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0002723265788517892</v>
+        <v>1.40922225000395e-06</v>
       </c>
       <c r="FT14" t="n">
-        <v>3.111476326012053e-05</v>
+        <v>3.967805696447613e-06</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0002428536681691185</v>
+        <v>6.030808208379312e-08</v>
       </c>
       <c r="FV14" t="n">
-        <v>7.982909301063046e-05</v>
+        <v>1.474039947879646e-07</v>
       </c>
       <c r="FW14" t="n">
-        <v>8.873403203324415e-07</v>
+        <v>4.079403879586607e-06</v>
       </c>
       <c r="FX14" t="n">
-        <v>8.96219426067546e-05</v>
+        <v>1.870885739663208e-07</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0003071661340072751</v>
+        <v>6.232333475963969e-07</v>
       </c>
       <c r="FZ14" t="n">
-        <v>8.165003237081692e-05</v>
+        <v>1.641509925320861e-06</v>
       </c>
       <c r="GA14" t="n">
-        <v>6.751508772140369e-05</v>
+        <v>2.432717565170606e-06</v>
       </c>
       <c r="GB14" t="n">
-        <v>1.665238960413262e-05</v>
+        <v>6.315553946478758e-08</v>
       </c>
       <c r="GC14" t="n">
-        <v>9.690553997643292e-05</v>
+        <v>3.058127049371251e-06</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0001629586913622916</v>
+        <v>2.686270363483345e-06</v>
       </c>
       <c r="GE14" t="n">
-        <v>1.806791988201439e-05</v>
+        <v>2.506860141693323e-07</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0001598936360096559</v>
+        <v>6.981475735301501e-07</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0001296707923756912</v>
+        <v>7.436117925863073e-07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.00167021865490824</v>
+        <v>0.0002845706476364285</v>
       </c>
       <c r="B15" t="n">
-        <v>9.457235137233511e-05</v>
+        <v>4.116450145374984e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0001039326598402113</v>
+        <v>0.0003513158881105483</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0004113095346838236</v>
+        <v>4.370500391814858e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>8.604559843661264e-05</v>
+        <v>0.0002429278974886984</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001741273095831275</v>
+        <v>0.0001889189588837326</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0002676239528227597</v>
+        <v>0.0001904700766317546</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0008560880087316036</v>
+        <v>9.807941387407482e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>3.276838469901122e-05</v>
+        <v>5.51759876543656e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001234577037394047</v>
+        <v>0.0002218269655713812</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0001699691492831334</v>
+        <v>0.0001012149587040767</v>
       </c>
       <c r="L15" t="n">
-        <v>2.443724952172488e-05</v>
+        <v>0.000335507036652416</v>
       </c>
       <c r="M15" t="n">
-        <v>0.000219470530282706</v>
+        <v>4.957719647791237e-05</v>
       </c>
       <c r="N15" t="n">
-        <v>0.000489481317345053</v>
+        <v>0.0002134509268216789</v>
       </c>
       <c r="O15" t="n">
-        <v>0.001377980457618833</v>
+        <v>0.0003517789882607758</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0006541566690430045</v>
+        <v>0.0001557462674099952</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.000984865939244628</v>
+        <v>7.422069029416889e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0001051660001394339</v>
+        <v>6.483511242549866e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0001898791088024154</v>
+        <v>9.546357614453882e-05</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0005104299052618444</v>
+        <v>0.0002309273986611515</v>
       </c>
       <c r="U15" t="n">
-        <v>3.203335654688999e-05</v>
+        <v>0.0001406455994583666</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0004628211027011275</v>
+        <v>0.0001050041464623064</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0006969345267862082</v>
+        <v>0.0001612154010217637</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0003153313009534031</v>
+        <v>0.0001811901020118967</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0003236066550016403</v>
+        <v>6.176505848998204e-05</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0001597583468537778</v>
+        <v>2.815273910528049e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.049503958318383e-05</v>
+        <v>2.70626405836083e-05</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0003404128656256944</v>
+        <v>5.058411989011802e-05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0003432836092542857</v>
+        <v>9.519295417703688e-05</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0001445720554329455</v>
+        <v>2.093514922307804e-06</v>
       </c>
       <c r="AE15" t="n">
-        <v>9.105939534492791e-05</v>
+        <v>4.054516466567293e-06</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.436747697880492e-05</v>
+        <v>5.25549694430083e-07</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0002059012185782194</v>
+        <v>4.096018892596476e-05</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.703036105027422e-05</v>
+        <v>8.404911932302639e-05</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0002679356839507818</v>
+        <v>2.126984327333048e-05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.354572593001649e-05</v>
+        <v>4.749907020595856e-05</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0003242402744945139</v>
+        <v>1.497523044236004e-05</v>
       </c>
       <c r="AL15" t="n">
-        <v>6.94378322805278e-05</v>
+        <v>0.0001532843452878296</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.000275331549346447</v>
+        <v>6.919736188137904e-05</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.000114569251309149</v>
+        <v>6.246727571124211e-05</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0001353005063720047</v>
+        <v>5.806615081382915e-05</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.333595668664202e-05</v>
+        <v>2.330707502551377e-05</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.0001418007013853639</v>
+        <v>7.192896009655669e-05</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.619181269546971e-05</v>
+        <v>5.161129956832156e-05</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.997238905460108e-05</v>
+        <v>4.475112655200064e-05</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0009070850792340934</v>
+        <v>2.136469083779957e-05</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.000221832815441303</v>
+        <v>3.331449261168018e-05</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.402916137129068e-06</v>
+        <v>0.0001664221053943038</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.0004851377452723682</v>
+        <v>7.248120527947322e-05</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.001159089268185198</v>
+        <v>7.020934572210535e-05</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.0007836536387912929</v>
+        <v>0.0001953776954906061</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.000214110070373863</v>
+        <v>5.746536407968961e-05</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.0004195109358988702</v>
+        <v>0.0001765969209372997</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.156238719588146e-05</v>
+        <v>6.356993981171399e-05</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.000372301583411172</v>
+        <v>0.0002097870601573959</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.0001624443248147145</v>
+        <v>7.369628292508423e-05</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.064738696906716e-05</v>
+        <v>4.100907972315326e-06</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.000129853084217757</v>
+        <v>2.306440728716552e-05</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.0003903942997567356</v>
+        <v>6.98645890224725e-05</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.0003902594035025686</v>
+        <v>9.912991663441062e-05</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.0003353790671098977</v>
+        <v>7.871654815971851e-05</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.0004055915051139891</v>
+        <v>0.000183473268407397</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.783356805797666e-05</v>
+        <v>1.36747785290936e-05</v>
       </c>
       <c r="BL15" t="n">
-        <v>2.205625605711248e-05</v>
+        <v>0.0001067290431819856</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.0002696837473195046</v>
+        <v>8.782050281297415e-05</v>
       </c>
       <c r="BN15" t="n">
-        <v>9.568194218445569e-05</v>
+        <v>0.0001613433560123667</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0004294213431421667</v>
+        <v>0.0001256528194062412</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0003837457334157079</v>
+        <v>0.0001683606387814507</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.100034857401624e-05</v>
+        <v>1.770026574376971e-05</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.0003631241852417588</v>
+        <v>1.418005194864236e-05</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.0004840173642151058</v>
+        <v>5.979699926683679e-05</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.000231667043408379</v>
+        <v>2.733158544288017e-05</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.0004505117249209434</v>
+        <v>3.774874494411051e-05</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.000261965295067057</v>
+        <v>0.000199053916730918</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.000180715651367791</v>
+        <v>0.0001503590756328776</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0002590147196315229</v>
+        <v>7.558496145065874e-05</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0005098658730275929</v>
+        <v>0.0001156370781245641</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.000585670059081167</v>
+        <v>0.000233451573876664</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.707853804575279e-05</v>
+        <v>7.526332410634495e-06</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0001970465818885714</v>
+        <v>2.223123556177597e-05</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.544131737318821e-05</v>
+        <v>3.954645217163488e-05</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0003249882720410824</v>
+        <v>6.48438508505933e-05</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.0002376708289375529</v>
+        <v>0.0001357399742119014</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.394972034380771e-05</v>
+        <v>7.506688416469842e-05</v>
       </c>
       <c r="CG15" t="n">
-        <v>1.570706444908865e-05</v>
+        <v>8.179075666703284e-05</v>
       </c>
       <c r="CH15" t="n">
-        <v>3.818058030446991e-05</v>
+        <v>5.263241473585367e-05</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.0002575337130110711</v>
+        <v>5.190487354411744e-05</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.672460686881095e-05</v>
+        <v>4.671094757213723e-06</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.0003021221491508186</v>
+        <v>3.474405821179971e-05</v>
       </c>
       <c r="CL15" t="n">
-        <v>3.335371002322063e-05</v>
+        <v>2.136584225809202e-05</v>
       </c>
       <c r="CM15" t="n">
-        <v>3.04564819089137e-05</v>
+        <v>2.517998109397013e-05</v>
       </c>
       <c r="CN15" t="n">
-        <v>8.544472802896053e-05</v>
+        <v>6.703023245790973e-05</v>
       </c>
       <c r="CO15" t="n">
-        <v>5.306265666149557e-05</v>
+        <v>7.228417962323874e-05</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.838301043084357e-05</v>
+        <v>4.121501842746511e-05</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0007699021953158081</v>
+        <v>6.838799163233489e-05</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.0001226038439199328</v>
+        <v>3.489452501526102e-05</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0002251061087008566</v>
+        <v>0.0001264276797883213</v>
       </c>
       <c r="CT15" t="n">
-        <v>6.472003587987274e-05</v>
+        <v>4.855604493059218e-05</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.0001393267011735588</v>
+        <v>1.282876110053621e-05</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.0002993880480062217</v>
+        <v>6.743473204551265e-05</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0002217972651124001</v>
+        <v>9.504622721578926e-05</v>
       </c>
       <c r="CX15" t="n">
-        <v>4.503293166635558e-05</v>
+        <v>6.342241249512881e-05</v>
       </c>
       <c r="CY15" t="n">
-        <v>9.8626253020484e-05</v>
+        <v>7.703118171775714e-05</v>
       </c>
       <c r="CZ15" t="n">
-        <v>3.361049311934039e-05</v>
+        <v>4.523683310253546e-05</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.0002509529876988381</v>
+        <v>5.475396028487012e-05</v>
       </c>
       <c r="DB15" t="n">
-        <v>9.168230462819338e-06</v>
+        <v>2.578637941041961e-05</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.000317820260534063</v>
+        <v>1.031508782034507e-05</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.331703944946639e-05</v>
+        <v>9.382628377352376e-06</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.0001015603847918101</v>
+        <v>8.372783486265689e-05</v>
       </c>
       <c r="DF15" t="n">
-        <v>4.186153091723099e-06</v>
+        <v>2.029938332270831e-05</v>
       </c>
       <c r="DG15" t="n">
-        <v>8.462984260404482e-05</v>
+        <v>8.753647853154689e-05</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0002712910354603082</v>
+        <v>9.287933062296361e-05</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.001021156320348382</v>
+        <v>0.0001209652400575578</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.0001048705671564676</v>
+        <v>6.690370355499908e-05</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.082425923319533e-05</v>
+        <v>3.196422039764002e-05</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.0004910093848593533</v>
+        <v>3.395717430976219e-05</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.0003435872786212713</v>
+        <v>1.992621764657088e-05</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.0001932077575474977</v>
+        <v>3.052259125979617e-05</v>
       </c>
       <c r="DO15" t="n">
-        <v>9.108742233365774e-05</v>
+        <v>5.519985643331893e-05</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.0001477284531574696</v>
+        <v>0.0001550452725496143</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.0002956194803118706</v>
+        <v>0.0001169196766568348</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.0002545712632127106</v>
+        <v>4.054810415254906e-05</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.0002335230819880962</v>
+        <v>0.0001163043634733185</v>
       </c>
       <c r="DT15" t="n">
-        <v>1.033703301800415e-05</v>
+        <v>4.192177584627643e-05</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.0004397512238938361</v>
+        <v>7.888139407441486e-06</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.0001359848247375339</v>
+        <v>7.391051894956036e-06</v>
       </c>
       <c r="DW15" t="n">
-        <v>2.156382834073156e-06</v>
+        <v>4.963086030329578e-05</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.000174379616510123</v>
+        <v>4.447580795385875e-05</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.831164450384676e-06</v>
+        <v>0.0002256112347822636</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.0001053648957167752</v>
+        <v>0.0001201660998049192</v>
       </c>
       <c r="EA15" t="n">
-        <v>6.966355431359261e-05</v>
+        <v>2.728130129980855e-05</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.0004054703167639673</v>
+        <v>0.0001241442805621773</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.0002119124983437359</v>
+        <v>2.072961251542438e-05</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.000367523287422955</v>
+        <v>2.55653740168782e-05</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.0001539886288810521</v>
+        <v>1.925789547385648e-06</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.0002663191989995539</v>
+        <v>3.364745498402044e-05</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0004039595078211278</v>
+        <v>0.0001899069757200778</v>
       </c>
       <c r="EH15" t="n">
-        <v>1.525594143458875e-05</v>
+        <v>1.849455293267965e-05</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0001829966640798375</v>
+        <v>5.304724982124753e-05</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0001377759617753327</v>
+        <v>0.0001031080755637959</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.0001358421868644655</v>
+        <v>6.546754775627051e-06</v>
       </c>
       <c r="EL15" t="n">
-        <v>4.225572774885222e-05</v>
+        <v>2.999361277034041e-05</v>
       </c>
       <c r="EM15" t="n">
-        <v>1.93957475858042e-05</v>
+        <v>4.254993109498173e-05</v>
       </c>
       <c r="EN15" t="n">
-        <v>6.253326864680275e-05</v>
+        <v>3.496760837151669e-05</v>
       </c>
       <c r="EO15" t="n">
-        <v>9.829392365645617e-05</v>
+        <v>4.722438825410791e-05</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0003070847596973181</v>
+        <v>0.0001221645652549341</v>
       </c>
       <c r="EQ15" t="n">
-        <v>7.616166840307415e-05</v>
+        <v>6.350100011331961e-05</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.000132653716718778</v>
+        <v>1.293811146751978e-05</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.0004557844949886203</v>
+        <v>3.061180905206129e-05</v>
       </c>
       <c r="ET15" t="n">
-        <v>8.481410623062402e-05</v>
+        <v>0.0001446355890948325</v>
       </c>
       <c r="EU15" t="n">
-        <v>2.369064895901829e-05</v>
+        <v>4.393735434859991e-05</v>
       </c>
       <c r="EV15" t="n">
-        <v>6.031319935573265e-05</v>
+        <v>0.0001642536517465487</v>
       </c>
       <c r="EW15" t="n">
-        <v>2.31600170081947e-05</v>
+        <v>4.494047607295215e-05</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.0002573538513388485</v>
+        <v>5.405039701145142e-05</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.0001832035486586392</v>
+        <v>9.381685958942398e-05</v>
       </c>
       <c r="EZ15" t="n">
-        <v>4.149982851231471e-05</v>
+        <v>5.841600795974955e-05</v>
       </c>
       <c r="FA15" t="n">
-        <v>7.206894224509597e-05</v>
+        <v>9.20398160815239e-05</v>
       </c>
       <c r="FB15" t="n">
-        <v>7.042604556772858e-05</v>
+        <v>6.559869507327676e-05</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.0002192361571360379</v>
+        <v>8.444026752840728e-05</v>
       </c>
       <c r="FD15" t="n">
-        <v>5.375863838708028e-05</v>
+        <v>1.181417610496283e-05</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0004133410402573645</v>
+        <v>4.956786142429337e-06</v>
       </c>
       <c r="FF15" t="n">
-        <v>5.782567313872278e-07</v>
+        <v>3.482586180325598e-06</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.0001954740146175027</v>
+        <v>0.0001010437117656693</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0002578626153990626</v>
+        <v>5.009950837120414e-05</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.000141154756420292</v>
+        <v>3.099008608842269e-05</v>
       </c>
       <c r="FJ15" t="n">
-        <v>6.83922553434968e-05</v>
+        <v>6.718456279486418e-05</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0001891303836600855</v>
+        <v>0.000169078863109462</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.0002186479250667617</v>
+        <v>0.0001702331937849522</v>
       </c>
       <c r="FM15" t="n">
-        <v>5.577541378443129e-05</v>
+        <v>5.207703361520544e-05</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.0001239460834767669</v>
+        <v>0.000123813355457969</v>
       </c>
       <c r="FO15" t="n">
-        <v>6.068305083317682e-06</v>
+        <v>5.254218922345899e-05</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0001530023582745343</v>
+        <v>3.392765938770026e-05</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.00013038631004747</v>
+        <v>0.0002019608800765127</v>
       </c>
       <c r="FR15" t="n">
-        <v>1.128824078477919e-05</v>
+        <v>0.0002510814229026437</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.0004744056495837867</v>
+        <v>2.407183637842536e-05</v>
       </c>
       <c r="FT15" t="n">
-        <v>2.861343455151655e-05</v>
+        <v>0.0003400120476726443</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0004335285630077124</v>
+        <v>5.441458051791415e-05</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.000273186044069007</v>
+        <v>0.0002336479956284165</v>
       </c>
       <c r="FW15" t="n">
-        <v>5.068710379418917e-05</v>
+        <v>8.208354120142758e-05</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.0001207228560815565</v>
+        <v>0.00012780494580511</v>
       </c>
       <c r="FY15" t="n">
-        <v>7.045459642540663e-05</v>
+        <v>3.680904046632349e-05</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0002105933090206236</v>
+        <v>5.894929927308112e-05</v>
       </c>
       <c r="GA15" t="n">
-        <v>2.326890535186976e-05</v>
+        <v>0.0001227341126650572</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.0001587430451763794</v>
+        <v>4.456578244571574e-05</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.0001496007316745818</v>
+        <v>3.791035123867914e-05</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.0003080392198171467</v>
+        <v>5.053302811575122e-05</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.0002867106813937426</v>
+        <v>4.514684769674204e-05</v>
       </c>
       <c r="GF15" t="n">
-        <v>4.808702215086669e-06</v>
+        <v>0.0002294382429681718</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.0001312531239818782</v>
+        <v>6.806275632698089e-05</v>
       </c>
     </row>
   </sheetData>
